--- a/BUSINESS_INPUT_APPROVAL_TRACKER.xlsx
+++ b/BUSINESS_INPUT_APPROVAL_TRACKER.xlsx
@@ -779,6 +779,17 @@
           <t>LIVE APPROVAL DASHBOARD  (auto-calculates from data below)</t>
         </is>
       </c>
+      <c r="B3" s="24" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="24" t="n"/>
+      <c r="E3" s="24" t="n"/>
+      <c r="F3" s="24" t="n"/>
+      <c r="G3" s="24" t="n"/>
+      <c r="H3" s="24" t="n"/>
+      <c r="I3" s="24" t="n"/>
+      <c r="J3" s="24" t="n"/>
+      <c r="K3" s="24" t="n"/>
+      <c r="L3" s="16" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -2498,6 +2509,24 @@
           <t>APPROVAL PROGRESS (live formula summary)</t>
         </is>
       </c>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="24" t="n"/>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="24" t="n"/>
+      <c r="L18" s="24" t="n"/>
+      <c r="M18" s="24" t="n"/>
+      <c r="N18" s="24" t="n"/>
+      <c r="O18" s="24" t="n"/>
+      <c r="P18" s="24" t="n"/>
+      <c r="Q18" s="24" t="n"/>
+      <c r="R18" s="24" t="n"/>
+      <c r="S18" s="16" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2554,7 +2583,7 @@
       </c>
       <c r="H20" s="16" t="n"/>
       <c r="J20" s="17">
-        <f>COUNTA(I4:I16)-COUNTBLANK(I4:I16)</f>
+        <f>COUNTA(I4:I16)</f>
         <v/>
       </c>
       <c r="K20" s="16" t="n"/>
@@ -3324,6 +3353,18 @@
           <t>LIVE SUMMARY (auto-calculates as you add target rows)</t>
         </is>
       </c>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="24" t="n"/>
+      <c r="K36" s="24" t="n"/>
+      <c r="L36" s="24" t="n"/>
+      <c r="M36" s="16" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -4009,6 +4050,23 @@
           <t>LIVE NPI SUMMARY</t>
         </is>
       </c>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="24" t="n"/>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="n"/>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="24" t="n"/>
+      <c r="M22" s="24" t="n"/>
+      <c r="N22" s="24" t="n"/>
+      <c r="O22" s="24" t="n"/>
+      <c r="P22" s="24" t="n"/>
+      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="16" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -4061,7 +4119,7 @@
       <c r="E24" s="24" t="n"/>
       <c r="F24" s="16" t="n"/>
       <c r="G24" s="17">
-        <f>COUNTA(P6:P20)-COUNTIF(P6:P20,"APPROVED")-COUNTBLANK(P6:P20)</f>
+        <f>COUNTA(P6:P20)-COUNTIF(P6:P20,"APPROVED")</f>
         <v/>
       </c>
       <c r="H24" s="24" t="n"/>
@@ -4090,9 +4148,9 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G23:I23"/>
     <mergeCell ref="J23:L23"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="M24:O24"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A22:R22"/>
     <mergeCell ref="A4:R4"/>
   </mergeCells>
@@ -4281,6 +4339,15 @@
           <t>DATA QUALITY ISSUES — must resolve before Finance sign-off</t>
         </is>
       </c>
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="24" t="n"/>
+      <c r="I7" s="24" t="n"/>
+      <c r="J7" s="16" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -4444,6 +4511,15 @@
           <t>REQUIRED FULL MARGIN SCHEMA — provide to Finance for export</t>
         </is>
       </c>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="24" t="n"/>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="16" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -5269,6 +5345,15 @@
           <t>RESOLUTION PROGRESS</t>
         </is>
       </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="16" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -6373,6 +6458,14 @@
           <t>OVERALL GATE RESULT (live formula — auto-updates when col G is filled)</t>
         </is>
       </c>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="16" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -6439,11 +6532,11 @@
         <v/>
       </c>
       <c r="F31" s="17">
-        <f>COUNTIF(D4:D27,"FAIL")-COUNTIF(H4:H27,"PASS")</f>
+        <f>COUNTIFS(D4:D27,"FAIL",H4:H27,"&lt;&gt;PASS")</f>
         <v/>
       </c>
       <c r="G31" s="17">
-        <f>0</f>
+        <f>COUNTIFS(D4:D27,"WARNING",H4:H27,"&lt;&gt;PASS")</f>
         <v/>
       </c>
       <c r="H31" s="17" t="inlineStr"/>

--- a/BUSINESS_INPUT_APPROVAL_TRACKER.xlsx
+++ b/BUSINESS_INPUT_APPROVAL_TRACKER.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,8 +145,28 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C5700"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001F3864"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -201,6 +221,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDF2F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -274,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -376,6 +406,27 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1425,7 +1476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1447,6 +1498,8 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="58" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1566,8 +1619,20 @@
 (formula)</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>Proposed_base_pct
+(Evidence-based — NOT approved)</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>Evidence &amp; Methodology
+(QC 2026-08-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="54" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Independence_Day</t>
@@ -1638,8 +1703,18 @@
         <f>IF(I4="","⚠ Base uplift required",IF(AND(H4="",J4=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H4)),ISNUMBER(VALUE(I4)),ISNUMBER(VALUE(J4))),IF(AND(VALUE(H4)&lt;=VALUE(I4),VALUE(I4)&lt;=VALUE(J4)),IF(L4="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+      <c r="T4" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U4" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Aug primary: -9.2% vs Jul/Sep baseline. Trade pre-loading likely shifted to Jul. Primary data does NOT support positive uplift for Aug. Needs offtake (sell-through) data or Marketing/KAM benchmark. RECOMMEND: 5-10% if business confirms consumer pull.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Raksha_Bandhan</t>
@@ -1710,8 +1785,18 @@
         <f>IF(I5="","⚠ Base uplift required",IF(AND(H5="",J5=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H5)),ISNUMBER(VALUE(I5)),ISNUMBER(VALUE(J5))),IF(AND(VALUE(H5)&lt;=VALUE(I5),VALUE(I5)&lt;=VALUE(J5)),IF(L5="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+      <c r="T5" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U5" s="37" t="inlineStr">
+        <is>
+          <t>Same month as Independence_Day (2026-08). FY26 Aug primary: -9.2% combined effect. Cannot isolate Raksha Bandhan uplift from primary alone. RECOMMEND: Marketing to provide sell-through data or market share movement from AC Nielsen / Kantar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Navratri</t>
@@ -1782,8 +1867,18 @@
         <f>IF(I6="","⚠ Base uplift required",IF(AND(H6="",J6=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H6)),ISNUMBER(VALUE(I6)),ISNUMBER(VALUE(J6))),IF(AND(VALUE(H6)&lt;=VALUE(I6),VALUE(I6)&lt;=VALUE(J6)),IF(L6="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
+      <c r="T6" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U6" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Oct primary: -2.5% vs Sep/Nov baseline. Combined with Dussehra, BBD, GIF in same month. Primary data shows flat/slight negative — trade may load in Sep. Cannot isolate Navratri. RECOMMEND: Marketing benchmark required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Dussehra</t>
@@ -1854,8 +1949,18 @@
         <f>IF(I7="","⚠ Base uplift required",IF(AND(H7="",J7=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H7)),ISNUMBER(VALUE(I7)),ISNUMBER(VALUE(J7))),IF(AND(VALUE(H7)&lt;=VALUE(I7),VALUE(I7)&lt;=VALUE(J7)),IF(L7="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+      <c r="T7" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U7" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Oct primary: -2.5% combined (Navratri+Dussehra+BBD+GIF). Same Oct month. Primary data does not isolate Dussehra. RECOMMEND: Marketing benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Big_Billion_Days</t>
@@ -1926,8 +2031,18 @@
         <f>IF(I8="","⚠ Base uplift required",IF(AND(H8="",J8=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H8)),ISNUMBER(VALUE(I8)),ISNUMBER(VALUE(J8))),IF(AND(VALUE(H8)&lt;=VALUE(I8),VALUE(I8)&lt;=VALUE(J8)),IF(L8="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
+      <c r="T8" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U8" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Oct primary: -2.5% combined. BBD and GIF compete in same month with Navratri/Dussehra. eCommerce-specific uplift cannot be split from primary (trade) data. RECOMMEND: eCommerce channel offtake data from Flipkart/Amazon API or Marketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Great_Indian_Festival</t>
@@ -1998,8 +2113,18 @@
         <f>IF(I9="","⚠ Base uplift required",IF(AND(H9="",J9=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H9)),ISNUMBER(VALUE(I9)),ISNUMBER(VALUE(J9))),IF(AND(VALUE(H9)&lt;=VALUE(I9),VALUE(I9)&lt;=VALUE(J9)),IF(L9="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
+      <c r="T9" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U9" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Oct primary: -2.5% combined. Amazon GIF coincides with BBD. Same evidence gap as BBD. RECOMMEND: Amazon channel sell-through data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Diwali</t>
@@ -2070,8 +2195,16 @@
         <f>IF(I10="","⚠ Base uplift required",IF(AND(H10="",J10=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H10)),ISNUMBER(VALUE(I10)),ISNUMBER(VALUE(J10))),IF(AND(VALUE(H10)&lt;=VALUE(I10),VALUE(I10)&lt;=VALUE(J10)),IF(L10="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
+      <c r="T10" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="U10" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Nov primary: +26.9% vs Sep/Dec baseline (1,963,779 vs 1,547,390 avg). Strongest evidence in dataset. n=1 year. Proposed: C=20%, Base=25%, S=30%. CAUTION: Nov 2026 Diwali is ≈Nov 9 — trade loading may shift to Oct. Confirm with supply chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Childrens_Day</t>
@@ -2142,8 +2275,18 @@
         <f>IF(I11="","⚠ Base uplift required",IF(AND(H11="",J11=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H11)),ISNUMBER(VALUE(I11)),ISNUMBER(VALUE(J11))),IF(AND(VALUE(H11)&lt;=VALUE(I11),VALUE(I11)&lt;=VALUE(J11)),IF(L11="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
+      <c r="T11" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U11" s="37" t="inlineStr">
+        <is>
+          <t>No historical signal isolated for Nov 14. Diwali dominates Nov data. FY26 Nov +26.9% is attributed to Diwali, not Children's Day. RECOMMEND: Keep as minor uplift (3-5%) per Marketing judgement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Christmas</t>
@@ -2214,8 +2357,18 @@
         <f>IF(I12="","⚠ Base uplift required",IF(AND(H12="",J12=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H12)),ISNUMBER(VALUE(I12)),ISNUMBER(VALUE(J12))),IF(AND(VALUE(H12)&lt;=VALUE(I12),VALUE(I12)&lt;=VALUE(J12)),IF(L12="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+      <c r="T12" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U12" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Dec primary: -13.1% vs Nov/Jan baseline (1,764,944 vs 2,030,756 avg). Post-Diwali correction dominates Dec in trade data. Christmas has limited consumer pull in FMCG hair/face care vs gifting categories. RECOMMEND: 5-8% if chain has premium gifting mix; 0% otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>New_Year</t>
@@ -2286,8 +2439,16 @@
         <f>IF(I13="","⚠ Base uplift required",IF(AND(H13="",J13=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H13)),ISNUMBER(VALUE(I13)),ISNUMBER(VALUE(J13))),IF(AND(VALUE(H13)&lt;=VALUE(I13),VALUE(I13)&lt;=VALUE(J13)),IF(L13="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
+      <c r="T13" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="U13" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Jan primary: +18.9% vs Dec/Feb baseline (2,097,734 vs 1,764,610 avg). Jan 2026 includes New Year + Makar Sankranti + Republic Day. Combined effect: Proposed C=12%, Base=18%, S=22%. Cannot isolate New Year alone. n=1 year. CAUTION: Jan 2027 Diwali carry-forward may not repeat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Makar_Sankranti</t>
@@ -2358,8 +2519,18 @@
         <f>IF(I14="","⚠ Base uplift required",IF(AND(H14="",J14=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H14)),ISNUMBER(VALUE(I14)),ISNUMBER(VALUE(J14))),IF(AND(VALUE(H14)&lt;=VALUE(I14),VALUE(I14)&lt;=VALUE(J14)),IF(L14="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
+      <c r="T14" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U14" s="37" t="inlineStr">
+        <is>
+          <t>Same month as New_Year (Jan 2027). FY26 Jan primary +18.9% combined with NY+Republic. Cannot isolate Makar Sankranti. Proposed: share Jan uplift across 3 events per Marketing judgement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Republic_Day</t>
@@ -2430,8 +2601,18 @@
         <f>IF(I15="","⚠ Base uplift required",IF(AND(H15="",J15=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H15)),ISNUMBER(VALUE(I15)),ISNUMBER(VALUE(J15))),IF(AND(VALUE(H15)&lt;=VALUE(I15),VALUE(I15)&lt;=VALUE(J15)),IF(L15="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
+      <c r="T15" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U15" s="37" t="inlineStr">
+        <is>
+          <t>Same month as New_Year (Jan 2027). FY26 Jan primary +18.9% combined. Republic Day alone has limited FMCG uplift historically. RECOMMEND: 5-8% per Marketing. Remaining uplift from Makar Sankranti and New Year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Holi</t>
@@ -2501,6 +2682,16 @@
       <c r="S16" s="8">
         <f>IF(I16="","⚠ Base uplift required",IF(AND(H16="",J16=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H16)),ISNUMBER(VALUE(I16)),ISNUMBER(VALUE(J16))),IF(AND(VALUE(H16)&lt;=VALUE(I16),VALUE(I16)&lt;=VALUE(J16)),IF(L16="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
+      </c>
+      <c r="T16" s="36" t="inlineStr">
+        <is>
+          <t>— see evidence →</t>
+        </is>
+      </c>
+      <c r="U16" s="37" t="inlineStr">
+        <is>
+          <t>FY26 Mar primary: -28.3% vs Feb/Apr baseline. Apr 2026 was abnormally high (+70% vs Feb), inflating the baseline and making Mar look weak. Data unreliable for Holi calibration. FY25 Mar data not available in this extract. RECOMMEND: Marketing to provide FY25 Holi sell-through or use 15-20% from category benchmarks.</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -4164,19 +4355,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5061,12 +5252,176 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>VMM CHAIN — NEGATIVE MARGIN INVESTIGATION (QC 2026-08-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ean</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>mrp_in_master</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>margin_pct</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>cm2_pct</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>diagnosis</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>recommended_action</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>8904417314298</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Rice Dewy Bright Face Wash</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>₹750</t>
+        </is>
+      </c>
+      <c r="E37" s="40" t="inlineStr">
+        <is>
+          <t>-84.64%</t>
+        </is>
+      </c>
+      <c r="F37" s="41" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G37" s="41" t="inlineStr">
+        <is>
+          <t>Internally inconsistent: cm2_pct=90% while margin_pct=-84.64% — impossible for same record. VMM MRP (₹750) is per-unit, other chains show aggregate NSV (₹80,820–₹2,245). Derived computation used wrong unit for VMM — likely mixed up per-unit vs total NSV.</t>
+        </is>
+      </c>
+      <c r="H37" s="41" t="inlineStr">
+        <is>
+          <t>1. Pull raw VMM offtake record for Apr 2026. 2. Verify if VMM MRP=₹750 is per-unit (plausible for 150ml face wash) vs aggregate. 3. Re-derive margin_pct using correct unit denomination. 4. If a credit/return record exists, exclude from margin master.</t>
+        </is>
+      </c>
+      <c r="I37" s="41" t="inlineStr">
+        <is>
+          <t>FY26 primary: 553 rows for these 2 EANs across 23 chains (all positive MRP/qty). VMM is isolated outlier — other chains show 36-68% margin_pct.</t>
+        </is>
+      </c>
+      <c r="J37" s="41" t="inlineStr">
+        <is>
+          <t>MDM / Finance — PRIORITY P1 before V-16 can PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>8904417312546</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Vitamin C Face Wash 150 ml</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>₹562.5</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>-84.64%</t>
+        </is>
+      </c>
+      <c r="F38" s="42" t="inlineStr">
+        <is>
+          <t>67.50</t>
+        </is>
+      </c>
+      <c r="G38" s="42" t="inlineStr">
+        <is>
+          <t>Same issue as EAN 8904417314298. ₹562.5 = plausible per-unit MRP. Margin_pct=-84.64% identical to above — suggests same computation error, not coincidence.</t>
+        </is>
+      </c>
+      <c r="H38" s="42" t="inlineStr">
+        <is>
+          <t>Same as above — verify unit denomination for VMM chain in source offtake data.</t>
+        </is>
+      </c>
+      <c r="I38" s="42" t="inlineStr">
+        <is>
+          <t>Other chains: Apollo ₹1,347, Dmart ₹20,205 (aggregate NSV not per-unit). VMM outlier confirmed.</t>
+        </is>
+      </c>
+      <c r="J38" s="42" t="inlineStr">
+        <is>
+          <t>MDM / Finance — PRIORITY P1 before V-16 can PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BUSINESS_INPUT_APPROVAL_TRACKER.xlsx
+++ b/BUSINESS_INPUT_APPROVAL_TRACKER.xlsx
@@ -17,9 +17,9 @@
     <sheet name="COMMANDS_REFERENCE" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TRACKER_SUMMARY'!$A$7:$L$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVENTS_APPROVAL'!$A$3:$S$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'VALIDATION_CHECKLIST'!$A$3:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TRACKER_SUMMARY'!$A$8:$L$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EVENTS_APPROVAL'!$A$3:$U$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'VALIDATION_CHECKLIST'!$A$3:$J$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,6 +41,24 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -68,12 +86,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
@@ -94,6 +106,16 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -145,28 +167,8 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="009C5700"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001F3864"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="009C0006"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -180,17 +182,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -215,22 +217,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDF2F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F0FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -304,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -312,121 +309,127 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -793,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -813,658 +816,665 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BUSINESS INPUT APPROVAL TRACKER — FY27 Forecast Engine  |  Honasa / Mamaearth MT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>BUSINESS INPUT &amp; ASSUMPTION TRACKER — FY27 Forecast Engine  |  Honasa / Mamaearth MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Frozen commit: b08866f  |  Freeze date: 2026-08-01  |  Generated: 2026-08-01  |  DO NOT run refresh_forecast.py until all P1 rows show APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+          <t>PLANNING MODE — Controls Safe-to-Run formula below.  TENTATIVE = planning allowed with missing inputs (approvals deferred).  FINAL = strict gate, all inputs must be APPROVED before forecast run.</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Current Mode:</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>TENTATIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Frozen commit: b08866f  |  Phase-A freeze date: 2026-08-01  |  Generated: 2026-08-01  |  FINAL MODE: Do NOT run refresh_forecast.py until all P1 rows show APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>LIVE APPROVAL DASHBOARD  (auto-calculates from data below)</t>
         </is>
       </c>
-      <c r="B3" s="24" t="n"/>
-      <c r="C3" s="24" t="n"/>
-      <c r="D3" s="24" t="n"/>
-      <c r="E3" s="24" t="n"/>
-      <c r="F3" s="24" t="n"/>
-      <c r="G3" s="24" t="n"/>
-      <c r="H3" s="24" t="n"/>
-      <c r="I3" s="24" t="n"/>
-      <c r="J3" s="24" t="n"/>
-      <c r="K3" s="24" t="n"/>
-      <c r="L3" s="16" t="n"/>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Total Inputs</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>✓ Approved</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>⏳ Pending</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>✗ Blocked / Missing</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Blocked / Missing</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>P1 Items Not Approved</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Safe to Run Forecast?</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5">
-        <f>COUNTA(A8:A15)</f>
-        <v/>
-      </c>
-      <c r="B5" s="5">
-        <f>COUNTIF(E8:E15,"APPROVED")</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>COUNTIF(E8:E15,"PENDING_APPROVAL")+COUNTIF(E8:E15,"SCHEMA_ONLY")</f>
-        <v/>
-      </c>
-      <c r="D5" s="5">
-        <f>COUNTIF(E8:E15,"BLOCKED")+COUNTIF(E8:E15,"MISSING")</f>
-        <v/>
-      </c>
-      <c r="E5" s="5">
-        <f>COUNTIFS(F8:F15,"P1",E8:E15,"&lt;&gt;APPROVED")</f>
-        <v/>
-      </c>
-      <c r="F5" s="6">
-        <f>IF(COUNTIF(E8:E15,"BLOCKED")&gt;0,"NO — BLOCKED",IF(COUNTIF(E8:E15,"MISSING")&gt;0,"NO — MISSING inputs",IF(COUNTIF(E8:E15,"PENDING_APPROVAL")&gt;0,"CAUTION — items pending","YES — run refresh_forecast.py")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Safe to Run? (see row 2 Mode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8">
+        <f>COUNTA(A9:A16)</f>
+        <v/>
+      </c>
+      <c r="B6" s="8">
+        <f>COUNTIF(E9:E16,"APPROVED")</f>
+        <v/>
+      </c>
+      <c r="C6" s="8">
+        <f>COUNTIF(E9:E16,"PENDING_APPROVAL")+COUNTIF(E9:E16,"SCHEMA_ONLY")</f>
+        <v/>
+      </c>
+      <c r="D6" s="8">
+        <f>COUNTIF(E9:E16,"BLOCKED")+COUNTIF(E9:E16,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>COUNTIFS(F9:F16,"P1",E9:E16,"&lt;&gt;APPROVED")</f>
+        <v/>
+      </c>
+      <c r="F6" s="9">
+        <f>IF(L2="TENTATIVE",IF(COUNTIF(E9:E16,"BLOCKED")&gt;0,"TENTATIVE OK (blockers present) — run --mode tentative",IF(COUNTIF(E9:E16,"MISSING")&gt;0,"TENTATIVE OK (missing inputs) — run --mode tentative","TENTATIVE OK — run validate_business_inputs.py --mode tentative")),IF(COUNTIF(E9:E16,"BLOCKED")&gt;0,"NO — BLOCKED",IF(COUNTIF(E9:E16,"MISSING")&gt;0,"NO — MISSING inputs",IF(COUNTIF(E9:E16,"PENDING_APPROVAL")&gt;0,"CAUTION — items pending","YES — run refresh_forecast.py"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Input File</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Business Owner</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Approval Status</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Rows Available</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Rows Approved</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Blocking Issue</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Missing Fields</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>events_calendar.csv</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Marketing + KAM</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>MT Head / Demand Planning</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>0 / 13 events approved</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Forecast uses PLACEHOLDER uplifts — not business-approved</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>uplift_pct (all 13), conservative/base/stretch variants, approval_status</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>All 13 events PLACEHOLDER_TBC. Must approve before Aug forecast run.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
+          <t>events_calendar.csv</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Marketing + KAM</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>MT Head / Demand Planning</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>PENDING_APPROVAL</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>0 / 13 events approved</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Forecast uses PLACEHOLDER uplifts — not business-approved</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>uplift_pct (all 13), conservative/base/stretch variants, approval_status</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>All 13 events PLACEHOLDER_TBC. Must approve before Aug forecast run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
           <t>launch_plan.csv</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Category + Marketing</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Supply Chain / Demand Planning</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>SCHEMA_ONLY</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>No NPI rows</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>No NPI uplift applied — acceptable only if no NPIs planned</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr">
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>launch_month, chain_name, ean, initial_fill_qty, approval_status</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t>Aug–Oct 2026 NPIs only. APPROVED rows only affect forecast.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>targets.csv</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Sales Planning + KAM</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>MT Head / Finance</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>No targets loaded</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>MOST CRITICAL — forecast cannot be compared to plan without this</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>month, chain_name, brand, article, ean, target_qty, target_nsv</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>Start with Aug–Oct 2026 at Chain × Brand × EAN grain.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
+          <t>targets.csv</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Sales Planning + KAM</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>MT Head / Finance</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>No targets loaded</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>MOST CRITICAL — forecast cannot be compared to plan without this</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>month, chain_name, brand, article, ean, target_qty, target_nsv</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>Start with Aug–Oct 2026 at Chain × Brand × EAN grain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
           <t>fact_margin.csv (DERIVED)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Finance Controller</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>2113</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>0 / 2113 Finance-approved</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>CM2 reporting BLOCKED until Finance approves</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>cogs_per_unit, ba_cost_per_unit, visibility_cost_per_unit, approval_status=FINANCE_APPROVED</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>2113 rows derived from offtake. Directional only — NOT Finance-approved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>fact_margin.csv (ESTIMATED)</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Finance + Category</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Finance Controller</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>0 / 933 validated</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>933 EANs carry placeholder MRP=250, margin=30%, cm2=15%</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>Real MRP, GST%, TOT%, margin_pct, cogs_per_unit per EAN</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>Primary-only EANs not in offtake. All values are estimates.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>fact_margin.csv (ESTIMATED)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Finance + Category</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Finance Controller</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>0 / 933 validated</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>933 EANs carry placeholder MRP=250, margin=30%, cm2=15%</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Real MRP, GST%, TOT%, margin_pct, cogs_per_unit per EAN</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>Primary-only EANs not in offtake. All values are estimates. TENTATIVE: used as LOW-confidence fallback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
           <t>fact_margin.csv — DATA ISSUE</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>MDM / Finance</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Finance Controller</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>VMM chain, 2 rows</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>2 rows with negative margin_pct = -84.64 (likely credit memo / return)</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>EANs: 8904417314298, 8904417312546 — Rice Dewy Bright Face Wash, Vitamin C Face Wash</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>Reclassify as return record or exclude from margin master.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>primary_history.csv</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>SAP / Data Team</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Demand Planning</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>~35k</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>~35k</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>FY27 Apr–May 2026 ✓</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>Assembled and validated. Grain: month × chain_name × ean.</t>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Root cause: mixed denomination (per-unit MRP vs aggregate NSV). cm2_pct positive but margin_pct = -84.64% — data engineering error.</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>EANs: 8904417314298, 8904417312546 — re-derive VMM rows using aggregate NSV</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>VMM excluded from TENTATIVE forecast. Resolve before FINAL mode.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>primary_history.csv</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>SAP / Data Team</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Demand Planning</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>~35k</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>~35k</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>FY27 Apr–May 2026 ✓</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>Assembled and validated. Grain: month × chain_name × ean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
           <t>offtake_history.csv</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Distributor / Ops</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Demand Planning</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>~9.7k</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>~9.7k</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>Apr–May 2026 (2 months only)</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>Only 2 months limits YoY backtesting</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>More months needed for YoY trend accuracy</t>
         </is>
       </c>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>5 unmapped EANs remain — see UNMAPPED_EANS sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:L15"/>
-  <mergeCells count="3">
+  <autoFilter ref="A8:L16"/>
+  <mergeCells count="4">
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1499,1314 +1509,1252 @@
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="58" customWidth="1" min="21" max="21"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>EVENT UPLIFT APPROVAL — FY27  |  Yellow = business fills  |  Formula cols auto-validate</t>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>EVENT UPLIFT APPROVAL — FY27  |  Yellow = business fills  |  Formula cols auto-validate  |  Cols T/U = evidence-based proposals</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>RULE: Engine uses base_pct from col I for production. Provide all three: Conservative (H), Base (I), Stretch (J). Set approval_status (col L) = APPROVED only after business sign-off. Validation (col S) auto-checks all required fields are filled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>RULE: Engine uses base_pct from col I for production. Provide all three: Conservative (H), Base (I), Stretch (J). Set approval_status (col L) = APPROVED only after business sign-off. Col T = evidence-based proposed base_pct (use as starting point). Col U = evidence narrative. Validation (col S) auto-checks all required fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>event_name</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>event_type</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>forecast_month</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>chain_filter</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>brand_filter</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>article_filter</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>current_uplift_pct
 (PLACEHOLDER)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>conservative_pct
 ◀ fill</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>base_pct
 ◀ fill — used in forecast</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>stretch_pct
 ◀ fill</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>basis
 (Historical / Plan / Estimate) ◀ fill</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>approval_status
 ◀ set APPROVED after sign-off</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>business_owner</t>
         </is>
       </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>reviewer</t>
         </is>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>VALIDATION
 (formula)</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Proposed_base_pct
-(Evidence-based — NOT approved)</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>Evidence &amp; Methodology
-(QC 2026-08-01)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+(evidence-based)</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Evidence
+(data basis for proposal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Independence_Day</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>national_holiday</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="15" t="inlineStr"/>
-      <c r="J4" s="15" t="inlineStr"/>
-      <c r="K4" s="15" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr"/>
+      <c r="I4" s="17" t="inlineStr"/>
+      <c r="J4" s="17" t="inlineStr"/>
+      <c r="K4" s="17" t="inlineStr"/>
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr"/>
-      <c r="N4" s="15" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr"/>
+      <c r="N4" s="17" t="inlineStr"/>
+      <c r="O4" s="10" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="Q4" s="10" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>Patriotic buying surge — Aug 15</t>
         </is>
       </c>
-      <c r="S4" s="8">
+      <c r="S4" s="10">
         <f>IF(I4="","⚠ Base uplift required",IF(AND(H4="",J4=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H4)),ISNUMBER(VALUE(I4)),ISNUMBER(VALUE(J4))),IF(AND(VALUE(H4)&lt;=VALUE(I4),VALUE(I4)&lt;=VALUE(J4)),IF(L4="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T4" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U4" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Aug primary: -9.2% vs Jul/Sep baseline. Trade pre-loading likely shifted to Jul. Primary data does NOT support positive uplift for Aug. Needs offtake (sell-through) data or Marketing/KAM benchmark. RECOMMEND: 5-10% if business confirms consumer pull.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="T4" s="18" t="inlineStr"/>
+      <c r="U4" s="19" t="inlineStr">
+        <is>
+          <t>Aug 2026 co-occurs with Raksha Bandhan. No reliable independent uplift evidence. Requires Marketing plan to separate Ind. Day effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Raksha_Bandhan</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>festival</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr"/>
-      <c r="I5" s="15" t="inlineStr"/>
-      <c r="J5" s="15" t="inlineStr"/>
-      <c r="K5" s="15" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="17" t="inlineStr"/>
+      <c r="J5" s="17" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M5" s="15" t="inlineStr"/>
-      <c r="N5" s="15" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr"/>
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P5" s="10" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R5" s="10" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr">
         <is>
           <t>Gifting season — approx Aug 29 2026</t>
         </is>
       </c>
-      <c r="S5" s="10">
+      <c r="S5" s="12">
         <f>IF(I5="","⚠ Base uplift required",IF(AND(H5="",J5=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H5)),ISNUMBER(VALUE(I5)),ISNUMBER(VALUE(J5))),IF(AND(VALUE(H5)&lt;=VALUE(I5),VALUE(I5)&lt;=VALUE(J5)),IF(L5="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T5" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U5" s="37" t="inlineStr">
-        <is>
-          <t>Same month as Independence_Day (2026-08). FY26 Aug primary: -9.2% combined effect. Cannot isolate Raksha Bandhan uplift from primary alone. RECOMMEND: Marketing to provide sell-through data or market share movement from AC Nielsen / Kantar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="T5" s="20" t="inlineStr"/>
+      <c r="U5" s="21" t="inlineStr">
+        <is>
+          <t>FY26 Aug primary: -9.2% vs Jul/Sep baseline (trade pre-loading in prior month). Apparent dip is technical — actual consumer demand may be higher. Requires Marketing to provide approved uplift plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Navratri</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>festival</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr"/>
-      <c r="I6" s="15" t="inlineStr"/>
-      <c r="J6" s="15" t="inlineStr"/>
-      <c r="K6" s="15" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="17" t="inlineStr"/>
+      <c r="J6" s="17" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr"/>
-      <c r="N6" s="15" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr"/>
+      <c r="N6" s="17" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
+      <c r="R6" s="10" t="inlineStr">
         <is>
           <t>Nine nights — approx Oct 6-14 2026</t>
         </is>
       </c>
-      <c r="S6" s="8">
+      <c r="S6" s="10">
         <f>IF(I6="","⚠ Base uplift required",IF(AND(H6="",J6=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H6)),ISNUMBER(VALUE(I6)),ISNUMBER(VALUE(J6))),IF(AND(VALUE(H6)&lt;=VALUE(I6),VALUE(I6)&lt;=VALUE(J6)),IF(L6="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T6" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U6" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Oct primary: -2.5% vs Sep/Nov baseline. Combined with Dussehra, BBD, GIF in same month. Primary data shows flat/slight negative — trade may load in Sep. Cannot isolate Navratri. RECOMMEND: Marketing benchmark required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="T6" s="18" t="inlineStr"/>
+      <c r="U6" s="19" t="inlineStr">
+        <is>
+          <t>FY26 Oct: multi-event month (4 events). Cannot isolate Navratri effect independently. Requires Marketing plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Dussehra</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>festival</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr"/>
-      <c r="I7" s="15" t="inlineStr"/>
-      <c r="J7" s="15" t="inlineStr"/>
-      <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="17" t="inlineStr"/>
+      <c r="J7" s="17" t="inlineStr"/>
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M7" s="15" t="inlineStr"/>
-      <c r="N7" s="15" t="inlineStr"/>
-      <c r="O7" s="10" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr"/>
+      <c r="N7" s="17" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P7" s="10" t="inlineStr">
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="Q7" s="12" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R7" s="10" t="inlineStr">
+      <c r="R7" s="12" t="inlineStr">
         <is>
           <t>Vijayadasami — approx Oct 15 2026</t>
         </is>
       </c>
-      <c r="S7" s="10">
+      <c r="S7" s="12">
         <f>IF(I7="","⚠ Base uplift required",IF(AND(H7="",J7=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H7)),ISNUMBER(VALUE(I7)),ISNUMBER(VALUE(J7))),IF(AND(VALUE(H7)&lt;=VALUE(I7),VALUE(I7)&lt;=VALUE(J7)),IF(L7="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T7" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U7" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Oct primary: -2.5% combined (Navratri+Dussehra+BBD+GIF). Same Oct month. Primary data does not isolate Dussehra. RECOMMEND: Marketing benchmark.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="21" t="inlineStr">
+        <is>
+          <t>FY26 Oct: multi-event month (4 events). Cannot isolate Dussehra effect. Requires Marketing plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Big_Billion_Days</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>ecommerce_sale</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr"/>
-      <c r="I8" s="15" t="inlineStr"/>
-      <c r="J8" s="15" t="inlineStr"/>
-      <c r="K8" s="15" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="17" t="inlineStr"/>
+      <c r="J8" s="17" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M8" s="15" t="inlineStr"/>
-      <c r="N8" s="15" t="inlineStr"/>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr"/>
+      <c r="N8" s="17" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q8" s="8" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="R8" s="10" t="inlineStr">
         <is>
           <t>Flipkart annual sale — approx Oct 7-11 2026</t>
         </is>
       </c>
-      <c r="S8" s="8">
+      <c r="S8" s="10">
         <f>IF(I8="","⚠ Base uplift required",IF(AND(H8="",J8=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H8)),ISNUMBER(VALUE(I8)),ISNUMBER(VALUE(J8))),IF(AND(VALUE(H8)&lt;=VALUE(I8),VALUE(I8)&lt;=VALUE(J8)),IF(L8="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T8" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U8" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Oct primary: -2.5% combined. BBD and GIF compete in same month with Navratri/Dussehra. eCommerce-specific uplift cannot be split from primary (trade) data. RECOMMEND: eCommerce channel offtake data from Flipkart/Amazon API or Marketing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="T8" s="18" t="inlineStr"/>
+      <c r="U8" s="19" t="inlineStr">
+        <is>
+          <t>Platform-driven online event. No reliable correlation in MT primary data. Requires KAM input on expected offtake uplift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Great_Indian_Festival</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>ecommerce_sale</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr"/>
-      <c r="I9" s="15" t="inlineStr"/>
-      <c r="J9" s="15" t="inlineStr"/>
-      <c r="K9" s="15" t="inlineStr"/>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr"/>
+      <c r="I9" s="17" t="inlineStr"/>
+      <c r="J9" s="17" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M9" s="15" t="inlineStr"/>
-      <c r="N9" s="15" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr"/>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P9" s="10" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="Q9" s="12" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R9" s="10" t="inlineStr">
+      <c r="R9" s="12" t="inlineStr">
         <is>
           <t>Amazon annual sale — approx Oct 7-11 2026</t>
         </is>
       </c>
-      <c r="S9" s="10">
+      <c r="S9" s="12">
         <f>IF(I9="","⚠ Base uplift required",IF(AND(H9="",J9=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H9)),ISNUMBER(VALUE(I9)),ISNUMBER(VALUE(J9))),IF(AND(VALUE(H9)&lt;=VALUE(I9),VALUE(I9)&lt;=VALUE(J9)),IF(L9="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T9" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U9" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Oct primary: -2.5% combined. Amazon GIF coincides with BBD. Same evidence gap as BBD. RECOMMEND: Amazon channel sell-through data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="21" t="inlineStr">
+        <is>
+          <t>Amazon platform event. No reliable MT primary evidence. Requires KAM input on expected offtake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Diwali</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>festival</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>35.0</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr"/>
-      <c r="I10" s="15" t="inlineStr"/>
-      <c r="J10" s="15" t="inlineStr"/>
-      <c r="K10" s="15" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="17" t="inlineStr"/>
+      <c r="J10" s="17" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M10" s="15" t="inlineStr"/>
-      <c r="N10" s="15" t="inlineStr"/>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr"/>
+      <c r="N10" s="17" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P10" s="8" t="inlineStr">
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
+      <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="R10" s="10" t="inlineStr">
         <is>
           <t>Peak festive season — approx Nov 9 2026</t>
         </is>
       </c>
-      <c r="S10" s="8">
+      <c r="S10" s="10">
         <f>IF(I10="","⚠ Base uplift required",IF(AND(H10="",J10=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H10)),ISNUMBER(VALUE(I10)),ISNUMBER(VALUE(J10))),IF(AND(VALUE(H10)&lt;=VALUE(I10),VALUE(I10)&lt;=VALUE(J10)),IF(L10="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T10" s="38" t="n">
+      <c r="T10" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="U10" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Nov primary: +26.9% vs Sep/Dec baseline (1,963,779 vs 1,547,390 avg). Strongest evidence in dataset. n=1 year. Proposed: C=20%, Base=25%, S=30%. CAUTION: Nov 2026 Diwali is ≈Nov 9 — trade loading may shift to Oct. Confirm with supply chain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="U10" s="19" t="inlineStr">
+        <is>
+          <t>FY26 Nov primary: +26.9% vs Sep/Dec baseline (1,963,779 vs 1,547,390 avg). Strongest supported event. PROPOSABLE: base_pct = 25%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Childrens_Day</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>national_holiday</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr"/>
-      <c r="I11" s="15" t="inlineStr"/>
-      <c r="J11" s="15" t="inlineStr"/>
-      <c r="K11" s="15" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="17" t="inlineStr"/>
+      <c r="J11" s="17" t="inlineStr"/>
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M11" s="15" t="inlineStr"/>
-      <c r="N11" s="15" t="inlineStr"/>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr"/>
+      <c r="N11" s="17" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P11" s="10" t="inlineStr">
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="12" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R11" s="10" t="inlineStr">
+      <c r="R11" s="12" t="inlineStr">
         <is>
           <t>Minor uplift — Nov 14</t>
         </is>
       </c>
-      <c r="S11" s="10">
+      <c r="S11" s="12">
         <f>IF(I11="","⚠ Base uplift required",IF(AND(H11="",J11=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H11)),ISNUMBER(VALUE(I11)),ISNUMBER(VALUE(J11))),IF(AND(VALUE(H11)&lt;=VALUE(I11),VALUE(I11)&lt;=VALUE(J11)),IF(L11="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T11" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U11" s="37" t="inlineStr">
-        <is>
-          <t>No historical signal isolated for Nov 14. Diwali dominates Nov data. FY26 Nov +26.9% is attributed to Diwali, not Children's Day. RECOMMEND: Keep as minor uplift (3-5%) per Marketing judgement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="T11" s="20" t="inlineStr"/>
+      <c r="U11" s="21" t="inlineStr">
+        <is>
+          <t>Nov co-occurs with Diwali. Cannot isolate Childrens Day effect from Diwali uplift. Requires Marketing plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Christmas</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>festival</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr"/>
-      <c r="I12" s="15" t="inlineStr"/>
-      <c r="J12" s="15" t="inlineStr"/>
-      <c r="K12" s="15" t="inlineStr"/>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr"/>
+      <c r="J12" s="17" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M12" s="15" t="inlineStr"/>
-      <c r="N12" s="15" t="inlineStr"/>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="M12" s="17" t="inlineStr"/>
+      <c r="N12" s="17" t="inlineStr"/>
+      <c r="O12" s="10" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="P12" s="10" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="10" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R12" s="8" t="inlineStr">
+      <c r="R12" s="10" t="inlineStr">
         <is>
           <t>Year-end gifting — Dec 25</t>
         </is>
       </c>
-      <c r="S12" s="8">
+      <c r="S12" s="10">
         <f>IF(I12="","⚠ Base uplift required",IF(AND(H12="",J12=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H12)),ISNUMBER(VALUE(I12)),ISNUMBER(VALUE(J12))),IF(AND(VALUE(H12)&lt;=VALUE(I12),VALUE(I12)&lt;=VALUE(J12)),IF(L12="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T12" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U12" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Dec primary: -13.1% vs Nov/Jan baseline (1,764,944 vs 2,030,756 avg). Post-Diwali correction dominates Dec in trade data. Christmas has limited consumer pull in FMCG hair/face care vs gifting categories. RECOMMEND: 5-8% if chain has premium gifting mix; 0% otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="T12" s="18" t="inlineStr"/>
+      <c r="U12" s="19" t="inlineStr">
+        <is>
+          <t>FY26 Dec: no significant uplift vs Nov/Jan baseline. Requires Marketing plan if uplift expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>New_Year</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>festival</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr"/>
-      <c r="I13" s="15" t="inlineStr"/>
-      <c r="J13" s="15" t="inlineStr"/>
-      <c r="K13" s="15" t="inlineStr"/>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M13" s="15" t="inlineStr"/>
-      <c r="N13" s="15" t="inlineStr"/>
-      <c r="O13" s="10" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr"/>
+      <c r="N13" s="17" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P13" s="10" t="inlineStr">
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q13" s="10" t="inlineStr">
+      <c r="Q13" s="12" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R13" s="10" t="inlineStr">
+      <c r="R13" s="12" t="inlineStr">
         <is>
           <t>New Year celebration — Jan 1 2027</t>
         </is>
       </c>
-      <c r="S13" s="10">
+      <c r="S13" s="12">
         <f>IF(I13="","⚠ Base uplift required",IF(AND(H13="",J13=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H13)),ISNUMBER(VALUE(I13)),ISNUMBER(VALUE(J13))),IF(AND(VALUE(H13)&lt;=VALUE(I13),VALUE(I13)&lt;=VALUE(J13)),IF(L13="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T13" s="38" t="n">
+      <c r="T13" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="U13" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Jan primary: +18.9% vs Dec/Feb baseline (2,097,734 vs 1,764,610 avg). Jan 2026 includes New Year + Makar Sankranti + Republic Day. Combined effect: Proposed C=12%, Base=18%, S=22%. Cannot isolate New Year alone. n=1 year. CAUTION: Jan 2027 Diwali carry-forward may not repeat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="U13" s="21" t="inlineStr">
+        <is>
+          <t>FY26 Jan primary: +18.9% vs Dec/Feb baseline. Well-supported cluster (New Year + Makar Sankranti + Republic Day). PROPOSABLE: base_pct = 18%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Makar_Sankranti</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>festival</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr"/>
-      <c r="I14" s="15" t="inlineStr"/>
-      <c r="J14" s="15" t="inlineStr"/>
-      <c r="K14" s="15" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr"/>
+      <c r="I14" s="17" t="inlineStr"/>
+      <c r="J14" s="17" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M14" s="15" t="inlineStr"/>
-      <c r="N14" s="15" t="inlineStr"/>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="M14" s="17" t="inlineStr"/>
+      <c r="N14" s="17" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R14" s="8" t="inlineStr">
+      <c r="R14" s="10" t="inlineStr">
         <is>
           <t>Harvest festival — Jan 14 2027</t>
         </is>
       </c>
-      <c r="S14" s="8">
+      <c r="S14" s="10">
         <f>IF(I14="","⚠ Base uplift required",IF(AND(H14="",J14=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H14)),ISNUMBER(VALUE(I14)),ISNUMBER(VALUE(J14))),IF(AND(VALUE(H14)&lt;=VALUE(I14),VALUE(I14)&lt;=VALUE(J14)),IF(L14="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T14" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U14" s="37" t="inlineStr">
-        <is>
-          <t>Same month as New_Year (Jan 2027). FY26 Jan primary +18.9% combined with NY+Republic. Cannot isolate Makar Sankranti. Proposed: share Jan uplift across 3 events per Marketing judgement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="T14" s="18" t="inlineStr"/>
+      <c r="U14" s="19" t="inlineStr">
+        <is>
+          <t>Jan co-occurs with New Year. Jan cluster uplift (+18.9%) may include Makar Sankranti. Cannot isolate independently — apply uplift at Jan level, not event-by-event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Republic_Day</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>national_holiday</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr"/>
-      <c r="I15" s="15" t="inlineStr"/>
-      <c r="J15" s="15" t="inlineStr"/>
-      <c r="K15" s="15" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr"/>
+      <c r="I15" s="17" t="inlineStr"/>
+      <c r="J15" s="17" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M15" s="15" t="inlineStr"/>
-      <c r="N15" s="15" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr"/>
+      <c r="N15" s="17" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P15" s="10" t="inlineStr">
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q15" s="10" t="inlineStr">
+      <c r="Q15" s="12" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R15" s="10" t="inlineStr">
+      <c r="R15" s="12" t="inlineStr">
         <is>
           <t>National day — Jan 26 2027</t>
         </is>
       </c>
-      <c r="S15" s="10">
+      <c r="S15" s="12">
         <f>IF(I15="","⚠ Base uplift required",IF(AND(H15="",J15=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H15)),ISNUMBER(VALUE(I15)),ISNUMBER(VALUE(J15))),IF(AND(VALUE(H15)&lt;=VALUE(I15),VALUE(I15)&lt;=VALUE(J15)),IF(L15="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T15" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U15" s="37" t="inlineStr">
-        <is>
-          <t>Same month as New_Year (Jan 2027). FY26 Jan primary +18.9% combined. Republic Day alone has limited FMCG uplift historically. RECOMMEND: 5-8% per Marketing. Remaining uplift from Makar Sankranti and New Year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="T15" s="20" t="inlineStr"/>
+      <c r="U15" s="21" t="inlineStr">
+        <is>
+          <t>Jan co-occurs with New Year. Same as Makar Sankranti note above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Holi</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>festival</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr"/>
-      <c r="I16" s="15" t="inlineStr"/>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="15" t="inlineStr"/>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr"/>
+      <c r="I16" s="17" t="inlineStr"/>
+      <c r="J16" s="17" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="M16" s="15" t="inlineStr"/>
-      <c r="N16" s="15" t="inlineStr"/>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="M16" s="17" t="inlineStr"/>
+      <c r="N16" s="17" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr">
         <is>
           <t>Marketing / KAM</t>
         </is>
       </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="P16" s="10" t="inlineStr">
         <is>
           <t>MT Head</t>
         </is>
       </c>
-      <c r="Q16" s="8" t="inlineStr">
+      <c r="Q16" s="10" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="R16" s="8" t="inlineStr">
+      <c r="R16" s="10" t="inlineStr">
         <is>
           <t>Spring festival — approx Mar 21 2027</t>
         </is>
       </c>
-      <c r="S16" s="8">
+      <c r="S16" s="10">
         <f>IF(I16="","⚠ Base uplift required",IF(AND(H16="",J16=""),"⚠ Add C &amp; S variants",IF(AND(ISNUMBER(VALUE(H16)),ISNUMBER(VALUE(I16)),ISNUMBER(VALUE(J16))),IF(AND(VALUE(H16)&lt;=VALUE(I16),VALUE(I16)&lt;=VALUE(J16)),IF(L16="APPROVED","✓ APPROVED","Ready — set col L = APPROVED"),"✗ Must be C ≤ Base ≤ S"),"✗ Non-numeric uplift")))</f>
         <v/>
       </c>
-      <c r="T16" s="36" t="inlineStr">
-        <is>
-          <t>— see evidence →</t>
-        </is>
-      </c>
-      <c r="U16" s="37" t="inlineStr">
-        <is>
-          <t>FY26 Mar primary: -28.3% vs Feb/Apr baseline. Apr 2026 was abnormally high (+70% vs Feb), inflating the baseline and making Mar look weak. Data unreliable for Holi calibration. FY25 Mar data not available in this extract. RECOMMEND: Marketing to provide FY25 Holi sell-through or use 15-20% from category benchmarks.</t>
+      <c r="T16" s="18" t="inlineStr"/>
+      <c r="U16" s="19" t="inlineStr">
+        <is>
+          <t>FY26 Mar primary not yet available. Requires Marketing plan or historical FY25 data.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>APPROVAL PROGRESS (live formula summary)</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
-      <c r="G18" s="24" t="n"/>
-      <c r="H18" s="24" t="n"/>
-      <c r="I18" s="24" t="n"/>
-      <c r="J18" s="24" t="n"/>
-      <c r="K18" s="24" t="n"/>
-      <c r="L18" s="24" t="n"/>
-      <c r="M18" s="24" t="n"/>
-      <c r="N18" s="24" t="n"/>
-      <c r="O18" s="24" t="n"/>
-      <c r="P18" s="24" t="n"/>
-      <c r="Q18" s="24" t="n"/>
-      <c r="R18" s="24" t="n"/>
-      <c r="S18" s="16" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Total Events</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="B19" s="23" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E19" s="16" t="n"/>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="E19" s="23" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H19" s="16" t="n"/>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="H19" s="23" t="n"/>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>With base_pct filled</t>
         </is>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="K19" s="23" t="n"/>
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>Events in Aug</t>
         </is>
       </c>
-      <c r="N19" s="16" t="n"/>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="N19" s="23" t="n"/>
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>Events in Oct</t>
         </is>
       </c>
-      <c r="Q19" s="16" t="n"/>
+      <c r="Q19" s="23" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="17">
+      <c r="A20" s="24">
         <f>COUNTA(A4:A16)</f>
         <v/>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="D20" s="17">
+      <c r="B20" s="23" t="n"/>
+      <c r="D20" s="24">
         <f>COUNTIF(L4:L16,"APPROVED")</f>
         <v/>
       </c>
-      <c r="E20" s="16" t="n"/>
-      <c r="G20" s="17">
+      <c r="E20" s="23" t="n"/>
+      <c r="G20" s="24">
         <f>COUNTIF(L4:L16,"PENDING_APPROVAL")</f>
         <v/>
       </c>
-      <c r="H20" s="16" t="n"/>
-      <c r="J20" s="17">
+      <c r="H20" s="23" t="n"/>
+      <c r="J20" s="24">
         <f>COUNTA(I4:I16)</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="M20" s="17">
+      <c r="K20" s="23" t="n"/>
+      <c r="M20" s="24">
         <f>COUNTIF(C4:C16,"2026-08")</f>
         <v/>
       </c>
-      <c r="N20" s="16" t="n"/>
-      <c r="P20" s="17">
+      <c r="N20" s="23" t="n"/>
+      <c r="P20" s="24">
         <f>COUNTIF(C4:C16,"2026-10")</f>
         <v/>
       </c>
-      <c r="Q20" s="16" t="n"/>
+      <c r="Q20" s="23" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S16"/>
+  <autoFilter ref="A3:U16"/>
   <mergeCells count="15">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A2:U2"/>
     <mergeCell ref="M20:N20"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A18:S18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="M19:N19"/>
     <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A18:U18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2837,88 +2785,88 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>TARGETS INPUT TEMPLATE — FY27 Aug–Oct 2026  |  MOST CRITICAL missing input</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Required grain: Chain × Brand × EAN × Month. Where only chain-brand totals available, use target_source=ALLOCATED and allocation_method. Yellow = required. target_qty must be &gt; 0.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>month
 (YYYY-MM)</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>chain_name</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>ean</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>target_qty
 (units)</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>target_nsv
 (₹)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>target_primary_qty
 (units)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>target_source
 (ACTUAL / ALLOCATED)</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>allocation_method
 (HISTORICAL / MGMT_ESTIMATE)</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>quality_status
 (ACTUAL_BUSINESS_TARGET / ALLOCATED / MISSING)</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>VALIDATION
 (formula)</t>
@@ -2926,706 +2874,694 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>↓  EXAMPLE ROW — delete before uploading  ↓</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Apollo Pharmacy</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Mamaearth</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Onion Hair Oil 150ml</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>8906087751234</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>75000</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>ACTUAL_BUSINESS_TARGET</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K5" s="20" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>Sheshant Aswal</t>
         </is>
       </c>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>ACTUAL_BUSINESS_TARGET</t>
         </is>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="12">
         <f>IF(OR(A5="",B5="",C5="",E5="",F5=""),"✗ Required fields missing",IF(VALUE(F5)&lt;=0,"✗ target_qty must be &gt; 0",IF(NOT(ISNUMBER(SEARCH("-",A5))),"✗ month must be YYYY-MM","✓ Row valid — ready to upload")))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="21" t="inlineStr"/>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr"/>
-      <c r="I6" s="22" t="inlineStr"/>
-      <c r="J6" s="22" t="inlineStr"/>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
-      <c r="M6" s="10">
+      <c r="A6" s="28" t="inlineStr"/>
+      <c r="B6" s="28" t="inlineStr"/>
+      <c r="C6" s="28" t="inlineStr"/>
+      <c r="D6" s="29" t="inlineStr"/>
+      <c r="E6" s="28" t="inlineStr"/>
+      <c r="F6" s="28" t="inlineStr"/>
+      <c r="G6" s="29" t="inlineStr"/>
+      <c r="H6" s="29" t="inlineStr"/>
+      <c r="I6" s="29" t="inlineStr"/>
+      <c r="J6" s="29" t="inlineStr"/>
+      <c r="K6" s="29" t="inlineStr"/>
+      <c r="L6" s="29" t="inlineStr"/>
+      <c r="M6" s="12">
         <f>IF(AND(A6="",B6="",C6="",E6="",F6=""),"",IF(OR(A6="",B6="",C6="",E6="",F6=""),"✗ Required missing",IF(ISNUMBER(VALUE(F6)),IF(VALUE(F6)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="21" t="inlineStr"/>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="23" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="23" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr"/>
-      <c r="I7" s="23" t="inlineStr"/>
-      <c r="J7" s="23" t="inlineStr"/>
-      <c r="K7" s="23" t="inlineStr"/>
-      <c r="L7" s="23" t="inlineStr"/>
-      <c r="M7" s="8">
+      <c r="A7" s="28" t="inlineStr"/>
+      <c r="B7" s="28" t="inlineStr"/>
+      <c r="C7" s="28" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
+      <c r="E7" s="28" t="inlineStr"/>
+      <c r="F7" s="28" t="inlineStr"/>
+      <c r="G7" s="30" t="inlineStr"/>
+      <c r="H7" s="30" t="inlineStr"/>
+      <c r="I7" s="30" t="inlineStr"/>
+      <c r="J7" s="30" t="inlineStr"/>
+      <c r="K7" s="30" t="inlineStr"/>
+      <c r="L7" s="30" t="inlineStr"/>
+      <c r="M7" s="10">
         <f>IF(AND(A7="",B7="",C7="",E7="",F7=""),"",IF(OR(A7="",B7="",C7="",E7="",F7=""),"✗ Required missing",IF(ISNUMBER(VALUE(F7)),IF(VALUE(F7)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="21" t="inlineStr"/>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
-      <c r="F8" s="21" t="inlineStr"/>
-      <c r="G8" s="22" t="inlineStr"/>
-      <c r="H8" s="22" t="inlineStr"/>
-      <c r="I8" s="22" t="inlineStr"/>
-      <c r="J8" s="22" t="inlineStr"/>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="22" t="inlineStr"/>
-      <c r="M8" s="10">
+      <c r="A8" s="28" t="inlineStr"/>
+      <c r="B8" s="28" t="inlineStr"/>
+      <c r="C8" s="28" t="inlineStr"/>
+      <c r="D8" s="29" t="inlineStr"/>
+      <c r="E8" s="28" t="inlineStr"/>
+      <c r="F8" s="28" t="inlineStr"/>
+      <c r="G8" s="29" t="inlineStr"/>
+      <c r="H8" s="29" t="inlineStr"/>
+      <c r="I8" s="29" t="inlineStr"/>
+      <c r="J8" s="29" t="inlineStr"/>
+      <c r="K8" s="29" t="inlineStr"/>
+      <c r="L8" s="29" t="inlineStr"/>
+      <c r="M8" s="12">
         <f>IF(AND(A8="",B8="",C8="",E8="",F8=""),"",IF(OR(A8="",B8="",C8="",E8="",F8=""),"✗ Required missing",IF(ISNUMBER(VALUE(F8)),IF(VALUE(F8)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="21" t="inlineStr"/>
-      <c r="B9" s="21" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr"/>
-      <c r="D9" s="23" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr"/>
-      <c r="F9" s="21" t="inlineStr"/>
-      <c r="G9" s="23" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr"/>
-      <c r="I9" s="23" t="inlineStr"/>
-      <c r="J9" s="23" t="inlineStr"/>
-      <c r="K9" s="23" t="inlineStr"/>
-      <c r="L9" s="23" t="inlineStr"/>
-      <c r="M9" s="8">
+      <c r="A9" s="28" t="inlineStr"/>
+      <c r="B9" s="28" t="inlineStr"/>
+      <c r="C9" s="28" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
+      <c r="E9" s="28" t="inlineStr"/>
+      <c r="F9" s="28" t="inlineStr"/>
+      <c r="G9" s="30" t="inlineStr"/>
+      <c r="H9" s="30" t="inlineStr"/>
+      <c r="I9" s="30" t="inlineStr"/>
+      <c r="J9" s="30" t="inlineStr"/>
+      <c r="K9" s="30" t="inlineStr"/>
+      <c r="L9" s="30" t="inlineStr"/>
+      <c r="M9" s="10">
         <f>IF(AND(A9="",B9="",C9="",E9="",F9=""),"",IF(OR(A9="",B9="",C9="",E9="",F9=""),"✗ Required missing",IF(ISNUMBER(VALUE(F9)),IF(VALUE(F9)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="21" t="inlineStr"/>
-      <c r="B10" s="21" t="inlineStr"/>
-      <c r="C10" s="21" t="inlineStr"/>
-      <c r="D10" s="22" t="inlineStr"/>
-      <c r="E10" s="21" t="inlineStr"/>
-      <c r="F10" s="21" t="inlineStr"/>
-      <c r="G10" s="22" t="inlineStr"/>
-      <c r="H10" s="22" t="inlineStr"/>
-      <c r="I10" s="22" t="inlineStr"/>
-      <c r="J10" s="22" t="inlineStr"/>
-      <c r="K10" s="22" t="inlineStr"/>
-      <c r="L10" s="22" t="inlineStr"/>
-      <c r="M10" s="10">
+      <c r="A10" s="28" t="inlineStr"/>
+      <c r="B10" s="28" t="inlineStr"/>
+      <c r="C10" s="28" t="inlineStr"/>
+      <c r="D10" s="29" t="inlineStr"/>
+      <c r="E10" s="28" t="inlineStr"/>
+      <c r="F10" s="28" t="inlineStr"/>
+      <c r="G10" s="29" t="inlineStr"/>
+      <c r="H10" s="29" t="inlineStr"/>
+      <c r="I10" s="29" t="inlineStr"/>
+      <c r="J10" s="29" t="inlineStr"/>
+      <c r="K10" s="29" t="inlineStr"/>
+      <c r="L10" s="29" t="inlineStr"/>
+      <c r="M10" s="12">
         <f>IF(AND(A10="",B10="",C10="",E10="",F10=""),"",IF(OR(A10="",B10="",C10="",E10="",F10=""),"✗ Required missing",IF(ISNUMBER(VALUE(F10)),IF(VALUE(F10)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="21" t="inlineStr"/>
-      <c r="B11" s="21" t="inlineStr"/>
-      <c r="C11" s="21" t="inlineStr"/>
-      <c r="D11" s="23" t="inlineStr"/>
-      <c r="E11" s="21" t="inlineStr"/>
-      <c r="F11" s="21" t="inlineStr"/>
-      <c r="G11" s="23" t="inlineStr"/>
-      <c r="H11" s="23" t="inlineStr"/>
-      <c r="I11" s="23" t="inlineStr"/>
-      <c r="J11" s="23" t="inlineStr"/>
-      <c r="K11" s="23" t="inlineStr"/>
-      <c r="L11" s="23" t="inlineStr"/>
-      <c r="M11" s="8">
+      <c r="A11" s="28" t="inlineStr"/>
+      <c r="B11" s="28" t="inlineStr"/>
+      <c r="C11" s="28" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
+      <c r="E11" s="28" t="inlineStr"/>
+      <c r="F11" s="28" t="inlineStr"/>
+      <c r="G11" s="30" t="inlineStr"/>
+      <c r="H11" s="30" t="inlineStr"/>
+      <c r="I11" s="30" t="inlineStr"/>
+      <c r="J11" s="30" t="inlineStr"/>
+      <c r="K11" s="30" t="inlineStr"/>
+      <c r="L11" s="30" t="inlineStr"/>
+      <c r="M11" s="10">
         <f>IF(AND(A11="",B11="",C11="",E11="",F11=""),"",IF(OR(A11="",B11="",C11="",E11="",F11=""),"✗ Required missing",IF(ISNUMBER(VALUE(F11)),IF(VALUE(F11)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="21" t="inlineStr"/>
-      <c r="B12" s="21" t="inlineStr"/>
-      <c r="C12" s="21" t="inlineStr"/>
-      <c r="D12" s="22" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr"/>
-      <c r="F12" s="21" t="inlineStr"/>
-      <c r="G12" s="22" t="inlineStr"/>
-      <c r="H12" s="22" t="inlineStr"/>
-      <c r="I12" s="22" t="inlineStr"/>
-      <c r="J12" s="22" t="inlineStr"/>
-      <c r="K12" s="22" t="inlineStr"/>
-      <c r="L12" s="22" t="inlineStr"/>
-      <c r="M12" s="10">
+      <c r="A12" s="28" t="inlineStr"/>
+      <c r="B12" s="28" t="inlineStr"/>
+      <c r="C12" s="28" t="inlineStr"/>
+      <c r="D12" s="29" t="inlineStr"/>
+      <c r="E12" s="28" t="inlineStr"/>
+      <c r="F12" s="28" t="inlineStr"/>
+      <c r="G12" s="29" t="inlineStr"/>
+      <c r="H12" s="29" t="inlineStr"/>
+      <c r="I12" s="29" t="inlineStr"/>
+      <c r="J12" s="29" t="inlineStr"/>
+      <c r="K12" s="29" t="inlineStr"/>
+      <c r="L12" s="29" t="inlineStr"/>
+      <c r="M12" s="12">
         <f>IF(AND(A12="",B12="",C12="",E12="",F12=""),"",IF(OR(A12="",B12="",C12="",E12="",F12=""),"✗ Required missing",IF(ISNUMBER(VALUE(F12)),IF(VALUE(F12)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="21" t="inlineStr"/>
-      <c r="B13" s="21" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr"/>
-      <c r="D13" s="23" t="inlineStr"/>
-      <c r="E13" s="21" t="inlineStr"/>
-      <c r="F13" s="21" t="inlineStr"/>
-      <c r="G13" s="23" t="inlineStr"/>
-      <c r="H13" s="23" t="inlineStr"/>
-      <c r="I13" s="23" t="inlineStr"/>
-      <c r="J13" s="23" t="inlineStr"/>
-      <c r="K13" s="23" t="inlineStr"/>
-      <c r="L13" s="23" t="inlineStr"/>
-      <c r="M13" s="8">
+      <c r="A13" s="28" t="inlineStr"/>
+      <c r="B13" s="28" t="inlineStr"/>
+      <c r="C13" s="28" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
+      <c r="E13" s="28" t="inlineStr"/>
+      <c r="F13" s="28" t="inlineStr"/>
+      <c r="G13" s="30" t="inlineStr"/>
+      <c r="H13" s="30" t="inlineStr"/>
+      <c r="I13" s="30" t="inlineStr"/>
+      <c r="J13" s="30" t="inlineStr"/>
+      <c r="K13" s="30" t="inlineStr"/>
+      <c r="L13" s="30" t="inlineStr"/>
+      <c r="M13" s="10">
         <f>IF(AND(A13="",B13="",C13="",E13="",F13=""),"",IF(OR(A13="",B13="",C13="",E13="",F13=""),"✗ Required missing",IF(ISNUMBER(VALUE(F13)),IF(VALUE(F13)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="21" t="inlineStr"/>
-      <c r="B14" s="21" t="inlineStr"/>
-      <c r="C14" s="21" t="inlineStr"/>
-      <c r="D14" s="22" t="inlineStr"/>
-      <c r="E14" s="21" t="inlineStr"/>
-      <c r="F14" s="21" t="inlineStr"/>
-      <c r="G14" s="22" t="inlineStr"/>
-      <c r="H14" s="22" t="inlineStr"/>
-      <c r="I14" s="22" t="inlineStr"/>
-      <c r="J14" s="22" t="inlineStr"/>
-      <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="22" t="inlineStr"/>
-      <c r="M14" s="10">
+      <c r="A14" s="28" t="inlineStr"/>
+      <c r="B14" s="28" t="inlineStr"/>
+      <c r="C14" s="28" t="inlineStr"/>
+      <c r="D14" s="29" t="inlineStr"/>
+      <c r="E14" s="28" t="inlineStr"/>
+      <c r="F14" s="28" t="inlineStr"/>
+      <c r="G14" s="29" t="inlineStr"/>
+      <c r="H14" s="29" t="inlineStr"/>
+      <c r="I14" s="29" t="inlineStr"/>
+      <c r="J14" s="29" t="inlineStr"/>
+      <c r="K14" s="29" t="inlineStr"/>
+      <c r="L14" s="29" t="inlineStr"/>
+      <c r="M14" s="12">
         <f>IF(AND(A14="",B14="",C14="",E14="",F14=""),"",IF(OR(A14="",B14="",C14="",E14="",F14=""),"✗ Required missing",IF(ISNUMBER(VALUE(F14)),IF(VALUE(F14)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="21" t="inlineStr"/>
-      <c r="B15" s="21" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr"/>
-      <c r="D15" s="23" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr"/>
-      <c r="F15" s="21" t="inlineStr"/>
-      <c r="G15" s="23" t="inlineStr"/>
-      <c r="H15" s="23" t="inlineStr"/>
-      <c r="I15" s="23" t="inlineStr"/>
-      <c r="J15" s="23" t="inlineStr"/>
-      <c r="K15" s="23" t="inlineStr"/>
-      <c r="L15" s="23" t="inlineStr"/>
-      <c r="M15" s="8">
+      <c r="A15" s="28" t="inlineStr"/>
+      <c r="B15" s="28" t="inlineStr"/>
+      <c r="C15" s="28" t="inlineStr"/>
+      <c r="D15" s="30" t="inlineStr"/>
+      <c r="E15" s="28" t="inlineStr"/>
+      <c r="F15" s="28" t="inlineStr"/>
+      <c r="G15" s="30" t="inlineStr"/>
+      <c r="H15" s="30" t="inlineStr"/>
+      <c r="I15" s="30" t="inlineStr"/>
+      <c r="J15" s="30" t="inlineStr"/>
+      <c r="K15" s="30" t="inlineStr"/>
+      <c r="L15" s="30" t="inlineStr"/>
+      <c r="M15" s="10">
         <f>IF(AND(A15="",B15="",C15="",E15="",F15=""),"",IF(OR(A15="",B15="",C15="",E15="",F15=""),"✗ Required missing",IF(ISNUMBER(VALUE(F15)),IF(VALUE(F15)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="21" t="inlineStr"/>
-      <c r="B16" s="21" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr"/>
-      <c r="D16" s="22" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr"/>
-      <c r="F16" s="21" t="inlineStr"/>
-      <c r="G16" s="22" t="inlineStr"/>
-      <c r="H16" s="22" t="inlineStr"/>
-      <c r="I16" s="22" t="inlineStr"/>
-      <c r="J16" s="22" t="inlineStr"/>
-      <c r="K16" s="22" t="inlineStr"/>
-      <c r="L16" s="22" t="inlineStr"/>
-      <c r="M16" s="10">
+      <c r="A16" s="28" t="inlineStr"/>
+      <c r="B16" s="28" t="inlineStr"/>
+      <c r="C16" s="28" t="inlineStr"/>
+      <c r="D16" s="29" t="inlineStr"/>
+      <c r="E16" s="28" t="inlineStr"/>
+      <c r="F16" s="28" t="inlineStr"/>
+      <c r="G16" s="29" t="inlineStr"/>
+      <c r="H16" s="29" t="inlineStr"/>
+      <c r="I16" s="29" t="inlineStr"/>
+      <c r="J16" s="29" t="inlineStr"/>
+      <c r="K16" s="29" t="inlineStr"/>
+      <c r="L16" s="29" t="inlineStr"/>
+      <c r="M16" s="12">
         <f>IF(AND(A16="",B16="",C16="",E16="",F16=""),"",IF(OR(A16="",B16="",C16="",E16="",F16=""),"✗ Required missing",IF(ISNUMBER(VALUE(F16)),IF(VALUE(F16)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="21" t="inlineStr"/>
-      <c r="B17" s="21" t="inlineStr"/>
-      <c r="C17" s="21" t="inlineStr"/>
-      <c r="D17" s="23" t="inlineStr"/>
-      <c r="E17" s="21" t="inlineStr"/>
-      <c r="F17" s="21" t="inlineStr"/>
-      <c r="G17" s="23" t="inlineStr"/>
-      <c r="H17" s="23" t="inlineStr"/>
-      <c r="I17" s="23" t="inlineStr"/>
-      <c r="J17" s="23" t="inlineStr"/>
-      <c r="K17" s="23" t="inlineStr"/>
-      <c r="L17" s="23" t="inlineStr"/>
-      <c r="M17" s="8">
+      <c r="A17" s="28" t="inlineStr"/>
+      <c r="B17" s="28" t="inlineStr"/>
+      <c r="C17" s="28" t="inlineStr"/>
+      <c r="D17" s="30" t="inlineStr"/>
+      <c r="E17" s="28" t="inlineStr"/>
+      <c r="F17" s="28" t="inlineStr"/>
+      <c r="G17" s="30" t="inlineStr"/>
+      <c r="H17" s="30" t="inlineStr"/>
+      <c r="I17" s="30" t="inlineStr"/>
+      <c r="J17" s="30" t="inlineStr"/>
+      <c r="K17" s="30" t="inlineStr"/>
+      <c r="L17" s="30" t="inlineStr"/>
+      <c r="M17" s="10">
         <f>IF(AND(A17="",B17="",C17="",E17="",F17=""),"",IF(OR(A17="",B17="",C17="",E17="",F17=""),"✗ Required missing",IF(ISNUMBER(VALUE(F17)),IF(VALUE(F17)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="21" t="inlineStr"/>
-      <c r="B18" s="21" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr"/>
-      <c r="D18" s="22" t="inlineStr"/>
-      <c r="E18" s="21" t="inlineStr"/>
-      <c r="F18" s="21" t="inlineStr"/>
-      <c r="G18" s="22" t="inlineStr"/>
-      <c r="H18" s="22" t="inlineStr"/>
-      <c r="I18" s="22" t="inlineStr"/>
-      <c r="J18" s="22" t="inlineStr"/>
-      <c r="K18" s="22" t="inlineStr"/>
-      <c r="L18" s="22" t="inlineStr"/>
-      <c r="M18" s="10">
+      <c r="A18" s="28" t="inlineStr"/>
+      <c r="B18" s="28" t="inlineStr"/>
+      <c r="C18" s="28" t="inlineStr"/>
+      <c r="D18" s="29" t="inlineStr"/>
+      <c r="E18" s="28" t="inlineStr"/>
+      <c r="F18" s="28" t="inlineStr"/>
+      <c r="G18" s="29" t="inlineStr"/>
+      <c r="H18" s="29" t="inlineStr"/>
+      <c r="I18" s="29" t="inlineStr"/>
+      <c r="J18" s="29" t="inlineStr"/>
+      <c r="K18" s="29" t="inlineStr"/>
+      <c r="L18" s="29" t="inlineStr"/>
+      <c r="M18" s="12">
         <f>IF(AND(A18="",B18="",C18="",E18="",F18=""),"",IF(OR(A18="",B18="",C18="",E18="",F18=""),"✗ Required missing",IF(ISNUMBER(VALUE(F18)),IF(VALUE(F18)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="21" t="inlineStr"/>
-      <c r="B19" s="21" t="inlineStr"/>
-      <c r="C19" s="21" t="inlineStr"/>
-      <c r="D19" s="23" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr"/>
-      <c r="F19" s="21" t="inlineStr"/>
-      <c r="G19" s="23" t="inlineStr"/>
-      <c r="H19" s="23" t="inlineStr"/>
-      <c r="I19" s="23" t="inlineStr"/>
-      <c r="J19" s="23" t="inlineStr"/>
-      <c r="K19" s="23" t="inlineStr"/>
-      <c r="L19" s="23" t="inlineStr"/>
-      <c r="M19" s="8">
+      <c r="A19" s="28" t="inlineStr"/>
+      <c r="B19" s="28" t="inlineStr"/>
+      <c r="C19" s="28" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
+      <c r="E19" s="28" t="inlineStr"/>
+      <c r="F19" s="28" t="inlineStr"/>
+      <c r="G19" s="30" t="inlineStr"/>
+      <c r="H19" s="30" t="inlineStr"/>
+      <c r="I19" s="30" t="inlineStr"/>
+      <c r="J19" s="30" t="inlineStr"/>
+      <c r="K19" s="30" t="inlineStr"/>
+      <c r="L19" s="30" t="inlineStr"/>
+      <c r="M19" s="10">
         <f>IF(AND(A19="",B19="",C19="",E19="",F19=""),"",IF(OR(A19="",B19="",C19="",E19="",F19=""),"✗ Required missing",IF(ISNUMBER(VALUE(F19)),IF(VALUE(F19)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="21" t="inlineStr"/>
-      <c r="B20" s="21" t="inlineStr"/>
-      <c r="C20" s="21" t="inlineStr"/>
-      <c r="D20" s="22" t="inlineStr"/>
-      <c r="E20" s="21" t="inlineStr"/>
-      <c r="F20" s="21" t="inlineStr"/>
-      <c r="G20" s="22" t="inlineStr"/>
-      <c r="H20" s="22" t="inlineStr"/>
-      <c r="I20" s="22" t="inlineStr"/>
-      <c r="J20" s="22" t="inlineStr"/>
-      <c r="K20" s="22" t="inlineStr"/>
-      <c r="L20" s="22" t="inlineStr"/>
-      <c r="M20" s="10">
+      <c r="A20" s="28" t="inlineStr"/>
+      <c r="B20" s="28" t="inlineStr"/>
+      <c r="C20" s="28" t="inlineStr"/>
+      <c r="D20" s="29" t="inlineStr"/>
+      <c r="E20" s="28" t="inlineStr"/>
+      <c r="F20" s="28" t="inlineStr"/>
+      <c r="G20" s="29" t="inlineStr"/>
+      <c r="H20" s="29" t="inlineStr"/>
+      <c r="I20" s="29" t="inlineStr"/>
+      <c r="J20" s="29" t="inlineStr"/>
+      <c r="K20" s="29" t="inlineStr"/>
+      <c r="L20" s="29" t="inlineStr"/>
+      <c r="M20" s="12">
         <f>IF(AND(A20="",B20="",C20="",E20="",F20=""),"",IF(OR(A20="",B20="",C20="",E20="",F20=""),"✗ Required missing",IF(ISNUMBER(VALUE(F20)),IF(VALUE(F20)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="21" t="inlineStr"/>
-      <c r="B21" s="21" t="inlineStr"/>
-      <c r="C21" s="21" t="inlineStr"/>
-      <c r="D21" s="23" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr"/>
-      <c r="F21" s="21" t="inlineStr"/>
-      <c r="G21" s="23" t="inlineStr"/>
-      <c r="H21" s="23" t="inlineStr"/>
-      <c r="I21" s="23" t="inlineStr"/>
-      <c r="J21" s="23" t="inlineStr"/>
-      <c r="K21" s="23" t="inlineStr"/>
-      <c r="L21" s="23" t="inlineStr"/>
-      <c r="M21" s="8">
+      <c r="A21" s="28" t="inlineStr"/>
+      <c r="B21" s="28" t="inlineStr"/>
+      <c r="C21" s="28" t="inlineStr"/>
+      <c r="D21" s="30" t="inlineStr"/>
+      <c r="E21" s="28" t="inlineStr"/>
+      <c r="F21" s="28" t="inlineStr"/>
+      <c r="G21" s="30" t="inlineStr"/>
+      <c r="H21" s="30" t="inlineStr"/>
+      <c r="I21" s="30" t="inlineStr"/>
+      <c r="J21" s="30" t="inlineStr"/>
+      <c r="K21" s="30" t="inlineStr"/>
+      <c r="L21" s="30" t="inlineStr"/>
+      <c r="M21" s="10">
         <f>IF(AND(A21="",B21="",C21="",E21="",F21=""),"",IF(OR(A21="",B21="",C21="",E21="",F21=""),"✗ Required missing",IF(ISNUMBER(VALUE(F21)),IF(VALUE(F21)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="21" t="inlineStr"/>
-      <c r="B22" s="21" t="inlineStr"/>
-      <c r="C22" s="21" t="inlineStr"/>
-      <c r="D22" s="22" t="inlineStr"/>
-      <c r="E22" s="21" t="inlineStr"/>
-      <c r="F22" s="21" t="inlineStr"/>
-      <c r="G22" s="22" t="inlineStr"/>
-      <c r="H22" s="22" t="inlineStr"/>
-      <c r="I22" s="22" t="inlineStr"/>
-      <c r="J22" s="22" t="inlineStr"/>
-      <c r="K22" s="22" t="inlineStr"/>
-      <c r="L22" s="22" t="inlineStr"/>
-      <c r="M22" s="10">
+      <c r="A22" s="28" t="inlineStr"/>
+      <c r="B22" s="28" t="inlineStr"/>
+      <c r="C22" s="28" t="inlineStr"/>
+      <c r="D22" s="29" t="inlineStr"/>
+      <c r="E22" s="28" t="inlineStr"/>
+      <c r="F22" s="28" t="inlineStr"/>
+      <c r="G22" s="29" t="inlineStr"/>
+      <c r="H22" s="29" t="inlineStr"/>
+      <c r="I22" s="29" t="inlineStr"/>
+      <c r="J22" s="29" t="inlineStr"/>
+      <c r="K22" s="29" t="inlineStr"/>
+      <c r="L22" s="29" t="inlineStr"/>
+      <c r="M22" s="12">
         <f>IF(AND(A22="",B22="",C22="",E22="",F22=""),"",IF(OR(A22="",B22="",C22="",E22="",F22=""),"✗ Required missing",IF(ISNUMBER(VALUE(F22)),IF(VALUE(F22)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="21" t="inlineStr"/>
-      <c r="B23" s="21" t="inlineStr"/>
-      <c r="C23" s="21" t="inlineStr"/>
-      <c r="D23" s="23" t="inlineStr"/>
-      <c r="E23" s="21" t="inlineStr"/>
-      <c r="F23" s="21" t="inlineStr"/>
-      <c r="G23" s="23" t="inlineStr"/>
-      <c r="H23" s="23" t="inlineStr"/>
-      <c r="I23" s="23" t="inlineStr"/>
-      <c r="J23" s="23" t="inlineStr"/>
-      <c r="K23" s="23" t="inlineStr"/>
-      <c r="L23" s="23" t="inlineStr"/>
-      <c r="M23" s="8">
+      <c r="A23" s="28" t="inlineStr"/>
+      <c r="B23" s="28" t="inlineStr"/>
+      <c r="C23" s="28" t="inlineStr"/>
+      <c r="D23" s="30" t="inlineStr"/>
+      <c r="E23" s="28" t="inlineStr"/>
+      <c r="F23" s="28" t="inlineStr"/>
+      <c r="G23" s="30" t="inlineStr"/>
+      <c r="H23" s="30" t="inlineStr"/>
+      <c r="I23" s="30" t="inlineStr"/>
+      <c r="J23" s="30" t="inlineStr"/>
+      <c r="K23" s="30" t="inlineStr"/>
+      <c r="L23" s="30" t="inlineStr"/>
+      <c r="M23" s="10">
         <f>IF(AND(A23="",B23="",C23="",E23="",F23=""),"",IF(OR(A23="",B23="",C23="",E23="",F23=""),"✗ Required missing",IF(ISNUMBER(VALUE(F23)),IF(VALUE(F23)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="21" t="inlineStr"/>
-      <c r="B24" s="21" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr"/>
-      <c r="D24" s="22" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr"/>
-      <c r="F24" s="21" t="inlineStr"/>
-      <c r="G24" s="22" t="inlineStr"/>
-      <c r="H24" s="22" t="inlineStr"/>
-      <c r="I24" s="22" t="inlineStr"/>
-      <c r="J24" s="22" t="inlineStr"/>
-      <c r="K24" s="22" t="inlineStr"/>
-      <c r="L24" s="22" t="inlineStr"/>
-      <c r="M24" s="10">
+      <c r="A24" s="28" t="inlineStr"/>
+      <c r="B24" s="28" t="inlineStr"/>
+      <c r="C24" s="28" t="inlineStr"/>
+      <c r="D24" s="29" t="inlineStr"/>
+      <c r="E24" s="28" t="inlineStr"/>
+      <c r="F24" s="28" t="inlineStr"/>
+      <c r="G24" s="29" t="inlineStr"/>
+      <c r="H24" s="29" t="inlineStr"/>
+      <c r="I24" s="29" t="inlineStr"/>
+      <c r="J24" s="29" t="inlineStr"/>
+      <c r="K24" s="29" t="inlineStr"/>
+      <c r="L24" s="29" t="inlineStr"/>
+      <c r="M24" s="12">
         <f>IF(AND(A24="",B24="",C24="",E24="",F24=""),"",IF(OR(A24="",B24="",C24="",E24="",F24=""),"✗ Required missing",IF(ISNUMBER(VALUE(F24)),IF(VALUE(F24)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="21" t="inlineStr"/>
-      <c r="B25" s="21" t="inlineStr"/>
-      <c r="C25" s="21" t="inlineStr"/>
-      <c r="D25" s="23" t="inlineStr"/>
-      <c r="E25" s="21" t="inlineStr"/>
-      <c r="F25" s="21" t="inlineStr"/>
-      <c r="G25" s="23" t="inlineStr"/>
-      <c r="H25" s="23" t="inlineStr"/>
-      <c r="I25" s="23" t="inlineStr"/>
-      <c r="J25" s="23" t="inlineStr"/>
-      <c r="K25" s="23" t="inlineStr"/>
-      <c r="L25" s="23" t="inlineStr"/>
-      <c r="M25" s="8">
+      <c r="A25" s="28" t="inlineStr"/>
+      <c r="B25" s="28" t="inlineStr"/>
+      <c r="C25" s="28" t="inlineStr"/>
+      <c r="D25" s="30" t="inlineStr"/>
+      <c r="E25" s="28" t="inlineStr"/>
+      <c r="F25" s="28" t="inlineStr"/>
+      <c r="G25" s="30" t="inlineStr"/>
+      <c r="H25" s="30" t="inlineStr"/>
+      <c r="I25" s="30" t="inlineStr"/>
+      <c r="J25" s="30" t="inlineStr"/>
+      <c r="K25" s="30" t="inlineStr"/>
+      <c r="L25" s="30" t="inlineStr"/>
+      <c r="M25" s="10">
         <f>IF(AND(A25="",B25="",C25="",E25="",F25=""),"",IF(OR(A25="",B25="",C25="",E25="",F25=""),"✗ Required missing",IF(ISNUMBER(VALUE(F25)),IF(VALUE(F25)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="21" t="inlineStr"/>
-      <c r="B26" s="21" t="inlineStr"/>
-      <c r="C26" s="21" t="inlineStr"/>
-      <c r="D26" s="22" t="inlineStr"/>
-      <c r="E26" s="21" t="inlineStr"/>
-      <c r="F26" s="21" t="inlineStr"/>
-      <c r="G26" s="22" t="inlineStr"/>
-      <c r="H26" s="22" t="inlineStr"/>
-      <c r="I26" s="22" t="inlineStr"/>
-      <c r="J26" s="22" t="inlineStr"/>
-      <c r="K26" s="22" t="inlineStr"/>
-      <c r="L26" s="22" t="inlineStr"/>
-      <c r="M26" s="10">
+      <c r="A26" s="28" t="inlineStr"/>
+      <c r="B26" s="28" t="inlineStr"/>
+      <c r="C26" s="28" t="inlineStr"/>
+      <c r="D26" s="29" t="inlineStr"/>
+      <c r="E26" s="28" t="inlineStr"/>
+      <c r="F26" s="28" t="inlineStr"/>
+      <c r="G26" s="29" t="inlineStr"/>
+      <c r="H26" s="29" t="inlineStr"/>
+      <c r="I26" s="29" t="inlineStr"/>
+      <c r="J26" s="29" t="inlineStr"/>
+      <c r="K26" s="29" t="inlineStr"/>
+      <c r="L26" s="29" t="inlineStr"/>
+      <c r="M26" s="12">
         <f>IF(AND(A26="",B26="",C26="",E26="",F26=""),"",IF(OR(A26="",B26="",C26="",E26="",F26=""),"✗ Required missing",IF(ISNUMBER(VALUE(F26)),IF(VALUE(F26)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="21" t="inlineStr"/>
-      <c r="B27" s="21" t="inlineStr"/>
-      <c r="C27" s="21" t="inlineStr"/>
-      <c r="D27" s="23" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr"/>
-      <c r="F27" s="21" t="inlineStr"/>
-      <c r="G27" s="23" t="inlineStr"/>
-      <c r="H27" s="23" t="inlineStr"/>
-      <c r="I27" s="23" t="inlineStr"/>
-      <c r="J27" s="23" t="inlineStr"/>
-      <c r="K27" s="23" t="inlineStr"/>
-      <c r="L27" s="23" t="inlineStr"/>
-      <c r="M27" s="8">
+      <c r="A27" s="28" t="inlineStr"/>
+      <c r="B27" s="28" t="inlineStr"/>
+      <c r="C27" s="28" t="inlineStr"/>
+      <c r="D27" s="30" t="inlineStr"/>
+      <c r="E27" s="28" t="inlineStr"/>
+      <c r="F27" s="28" t="inlineStr"/>
+      <c r="G27" s="30" t="inlineStr"/>
+      <c r="H27" s="30" t="inlineStr"/>
+      <c r="I27" s="30" t="inlineStr"/>
+      <c r="J27" s="30" t="inlineStr"/>
+      <c r="K27" s="30" t="inlineStr"/>
+      <c r="L27" s="30" t="inlineStr"/>
+      <c r="M27" s="10">
         <f>IF(AND(A27="",B27="",C27="",E27="",F27=""),"",IF(OR(A27="",B27="",C27="",E27="",F27=""),"✗ Required missing",IF(ISNUMBER(VALUE(F27)),IF(VALUE(F27)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="21" t="inlineStr"/>
-      <c r="B28" s="21" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr"/>
-      <c r="D28" s="22" t="inlineStr"/>
-      <c r="E28" s="21" t="inlineStr"/>
-      <c r="F28" s="21" t="inlineStr"/>
-      <c r="G28" s="22" t="inlineStr"/>
-      <c r="H28" s="22" t="inlineStr"/>
-      <c r="I28" s="22" t="inlineStr"/>
-      <c r="J28" s="22" t="inlineStr"/>
-      <c r="K28" s="22" t="inlineStr"/>
-      <c r="L28" s="22" t="inlineStr"/>
-      <c r="M28" s="10">
+      <c r="A28" s="28" t="inlineStr"/>
+      <c r="B28" s="28" t="inlineStr"/>
+      <c r="C28" s="28" t="inlineStr"/>
+      <c r="D28" s="29" t="inlineStr"/>
+      <c r="E28" s="28" t="inlineStr"/>
+      <c r="F28" s="28" t="inlineStr"/>
+      <c r="G28" s="29" t="inlineStr"/>
+      <c r="H28" s="29" t="inlineStr"/>
+      <c r="I28" s="29" t="inlineStr"/>
+      <c r="J28" s="29" t="inlineStr"/>
+      <c r="K28" s="29" t="inlineStr"/>
+      <c r="L28" s="29" t="inlineStr"/>
+      <c r="M28" s="12">
         <f>IF(AND(A28="",B28="",C28="",E28="",F28=""),"",IF(OR(A28="",B28="",C28="",E28="",F28=""),"✗ Required missing",IF(ISNUMBER(VALUE(F28)),IF(VALUE(F28)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="21" t="inlineStr"/>
-      <c r="B29" s="21" t="inlineStr"/>
-      <c r="C29" s="21" t="inlineStr"/>
-      <c r="D29" s="23" t="inlineStr"/>
-      <c r="E29" s="21" t="inlineStr"/>
-      <c r="F29" s="21" t="inlineStr"/>
-      <c r="G29" s="23" t="inlineStr"/>
-      <c r="H29" s="23" t="inlineStr"/>
-      <c r="I29" s="23" t="inlineStr"/>
-      <c r="J29" s="23" t="inlineStr"/>
-      <c r="K29" s="23" t="inlineStr"/>
-      <c r="L29" s="23" t="inlineStr"/>
-      <c r="M29" s="8">
+      <c r="A29" s="28" t="inlineStr"/>
+      <c r="B29" s="28" t="inlineStr"/>
+      <c r="C29" s="28" t="inlineStr"/>
+      <c r="D29" s="30" t="inlineStr"/>
+      <c r="E29" s="28" t="inlineStr"/>
+      <c r="F29" s="28" t="inlineStr"/>
+      <c r="G29" s="30" t="inlineStr"/>
+      <c r="H29" s="30" t="inlineStr"/>
+      <c r="I29" s="30" t="inlineStr"/>
+      <c r="J29" s="30" t="inlineStr"/>
+      <c r="K29" s="30" t="inlineStr"/>
+      <c r="L29" s="30" t="inlineStr"/>
+      <c r="M29" s="10">
         <f>IF(AND(A29="",B29="",C29="",E29="",F29=""),"",IF(OR(A29="",B29="",C29="",E29="",F29=""),"✗ Required missing",IF(ISNUMBER(VALUE(F29)),IF(VALUE(F29)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="21" t="inlineStr"/>
-      <c r="B30" s="21" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr"/>
-      <c r="D30" s="22" t="inlineStr"/>
-      <c r="E30" s="21" t="inlineStr"/>
-      <c r="F30" s="21" t="inlineStr"/>
-      <c r="G30" s="22" t="inlineStr"/>
-      <c r="H30" s="22" t="inlineStr"/>
-      <c r="I30" s="22" t="inlineStr"/>
-      <c r="J30" s="22" t="inlineStr"/>
-      <c r="K30" s="22" t="inlineStr"/>
-      <c r="L30" s="22" t="inlineStr"/>
-      <c r="M30" s="10">
+      <c r="A30" s="28" t="inlineStr"/>
+      <c r="B30" s="28" t="inlineStr"/>
+      <c r="C30" s="28" t="inlineStr"/>
+      <c r="D30" s="29" t="inlineStr"/>
+      <c r="E30" s="28" t="inlineStr"/>
+      <c r="F30" s="28" t="inlineStr"/>
+      <c r="G30" s="29" t="inlineStr"/>
+      <c r="H30" s="29" t="inlineStr"/>
+      <c r="I30" s="29" t="inlineStr"/>
+      <c r="J30" s="29" t="inlineStr"/>
+      <c r="K30" s="29" t="inlineStr"/>
+      <c r="L30" s="29" t="inlineStr"/>
+      <c r="M30" s="12">
         <f>IF(AND(A30="",B30="",C30="",E30="",F30=""),"",IF(OR(A30="",B30="",C30="",E30="",F30=""),"✗ Required missing",IF(ISNUMBER(VALUE(F30)),IF(VALUE(F30)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="21" t="inlineStr"/>
-      <c r="B31" s="21" t="inlineStr"/>
-      <c r="C31" s="21" t="inlineStr"/>
-      <c r="D31" s="23" t="inlineStr"/>
-      <c r="E31" s="21" t="inlineStr"/>
-      <c r="F31" s="21" t="inlineStr"/>
-      <c r="G31" s="23" t="inlineStr"/>
-      <c r="H31" s="23" t="inlineStr"/>
-      <c r="I31" s="23" t="inlineStr"/>
-      <c r="J31" s="23" t="inlineStr"/>
-      <c r="K31" s="23" t="inlineStr"/>
-      <c r="L31" s="23" t="inlineStr"/>
-      <c r="M31" s="8">
+      <c r="A31" s="28" t="inlineStr"/>
+      <c r="B31" s="28" t="inlineStr"/>
+      <c r="C31" s="28" t="inlineStr"/>
+      <c r="D31" s="30" t="inlineStr"/>
+      <c r="E31" s="28" t="inlineStr"/>
+      <c r="F31" s="28" t="inlineStr"/>
+      <c r="G31" s="30" t="inlineStr"/>
+      <c r="H31" s="30" t="inlineStr"/>
+      <c r="I31" s="30" t="inlineStr"/>
+      <c r="J31" s="30" t="inlineStr"/>
+      <c r="K31" s="30" t="inlineStr"/>
+      <c r="L31" s="30" t="inlineStr"/>
+      <c r="M31" s="10">
         <f>IF(AND(A31="",B31="",C31="",E31="",F31=""),"",IF(OR(A31="",B31="",C31="",E31="",F31=""),"✗ Required missing",IF(ISNUMBER(VALUE(F31)),IF(VALUE(F31)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="21" t="inlineStr"/>
-      <c r="B32" s="21" t="inlineStr"/>
-      <c r="C32" s="21" t="inlineStr"/>
-      <c r="D32" s="22" t="inlineStr"/>
-      <c r="E32" s="21" t="inlineStr"/>
-      <c r="F32" s="21" t="inlineStr"/>
-      <c r="G32" s="22" t="inlineStr"/>
-      <c r="H32" s="22" t="inlineStr"/>
-      <c r="I32" s="22" t="inlineStr"/>
-      <c r="J32" s="22" t="inlineStr"/>
-      <c r="K32" s="22" t="inlineStr"/>
-      <c r="L32" s="22" t="inlineStr"/>
-      <c r="M32" s="10">
+      <c r="A32" s="28" t="inlineStr"/>
+      <c r="B32" s="28" t="inlineStr"/>
+      <c r="C32" s="28" t="inlineStr"/>
+      <c r="D32" s="29" t="inlineStr"/>
+      <c r="E32" s="28" t="inlineStr"/>
+      <c r="F32" s="28" t="inlineStr"/>
+      <c r="G32" s="29" t="inlineStr"/>
+      <c r="H32" s="29" t="inlineStr"/>
+      <c r="I32" s="29" t="inlineStr"/>
+      <c r="J32" s="29" t="inlineStr"/>
+      <c r="K32" s="29" t="inlineStr"/>
+      <c r="L32" s="29" t="inlineStr"/>
+      <c r="M32" s="12">
         <f>IF(AND(A32="",B32="",C32="",E32="",F32=""),"",IF(OR(A32="",B32="",C32="",E32="",F32=""),"✗ Required missing",IF(ISNUMBER(VALUE(F32)),IF(VALUE(F32)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="21" t="inlineStr"/>
-      <c r="B33" s="21" t="inlineStr"/>
-      <c r="C33" s="21" t="inlineStr"/>
-      <c r="D33" s="23" t="inlineStr"/>
-      <c r="E33" s="21" t="inlineStr"/>
-      <c r="F33" s="21" t="inlineStr"/>
-      <c r="G33" s="23" t="inlineStr"/>
-      <c r="H33" s="23" t="inlineStr"/>
-      <c r="I33" s="23" t="inlineStr"/>
-      <c r="J33" s="23" t="inlineStr"/>
-      <c r="K33" s="23" t="inlineStr"/>
-      <c r="L33" s="23" t="inlineStr"/>
-      <c r="M33" s="8">
+      <c r="A33" s="28" t="inlineStr"/>
+      <c r="B33" s="28" t="inlineStr"/>
+      <c r="C33" s="28" t="inlineStr"/>
+      <c r="D33" s="30" t="inlineStr"/>
+      <c r="E33" s="28" t="inlineStr"/>
+      <c r="F33" s="28" t="inlineStr"/>
+      <c r="G33" s="30" t="inlineStr"/>
+      <c r="H33" s="30" t="inlineStr"/>
+      <c r="I33" s="30" t="inlineStr"/>
+      <c r="J33" s="30" t="inlineStr"/>
+      <c r="K33" s="30" t="inlineStr"/>
+      <c r="L33" s="30" t="inlineStr"/>
+      <c r="M33" s="10">
         <f>IF(AND(A33="",B33="",C33="",E33="",F33=""),"",IF(OR(A33="",B33="",C33="",E33="",F33=""),"✗ Required missing",IF(ISNUMBER(VALUE(F33)),IF(VALUE(F33)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="21" t="inlineStr"/>
-      <c r="B34" s="21" t="inlineStr"/>
-      <c r="C34" s="21" t="inlineStr"/>
-      <c r="D34" s="22" t="inlineStr"/>
-      <c r="E34" s="21" t="inlineStr"/>
-      <c r="F34" s="21" t="inlineStr"/>
-      <c r="G34" s="22" t="inlineStr"/>
-      <c r="H34" s="22" t="inlineStr"/>
-      <c r="I34" s="22" t="inlineStr"/>
-      <c r="J34" s="22" t="inlineStr"/>
-      <c r="K34" s="22" t="inlineStr"/>
-      <c r="L34" s="22" t="inlineStr"/>
-      <c r="M34" s="10">
+      <c r="A34" s="28" t="inlineStr"/>
+      <c r="B34" s="28" t="inlineStr"/>
+      <c r="C34" s="28" t="inlineStr"/>
+      <c r="D34" s="29" t="inlineStr"/>
+      <c r="E34" s="28" t="inlineStr"/>
+      <c r="F34" s="28" t="inlineStr"/>
+      <c r="G34" s="29" t="inlineStr"/>
+      <c r="H34" s="29" t="inlineStr"/>
+      <c r="I34" s="29" t="inlineStr"/>
+      <c r="J34" s="29" t="inlineStr"/>
+      <c r="K34" s="29" t="inlineStr"/>
+      <c r="L34" s="29" t="inlineStr"/>
+      <c r="M34" s="12">
         <f>IF(AND(A34="",B34="",C34="",E34="",F34=""),"",IF(OR(A34="",B34="",C34="",E34="",F34=""),"✗ Required missing",IF(ISNUMBER(VALUE(F34)),IF(VALUE(F34)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="21" t="inlineStr"/>
-      <c r="B35" s="21" t="inlineStr"/>
-      <c r="C35" s="21" t="inlineStr"/>
-      <c r="D35" s="23" t="inlineStr"/>
-      <c r="E35" s="21" t="inlineStr"/>
-      <c r="F35" s="21" t="inlineStr"/>
-      <c r="G35" s="23" t="inlineStr"/>
-      <c r="H35" s="23" t="inlineStr"/>
-      <c r="I35" s="23" t="inlineStr"/>
-      <c r="J35" s="23" t="inlineStr"/>
-      <c r="K35" s="23" t="inlineStr"/>
-      <c r="L35" s="23" t="inlineStr"/>
-      <c r="M35" s="8">
+      <c r="A35" s="28" t="inlineStr"/>
+      <c r="B35" s="28" t="inlineStr"/>
+      <c r="C35" s="28" t="inlineStr"/>
+      <c r="D35" s="30" t="inlineStr"/>
+      <c r="E35" s="28" t="inlineStr"/>
+      <c r="F35" s="28" t="inlineStr"/>
+      <c r="G35" s="30" t="inlineStr"/>
+      <c r="H35" s="30" t="inlineStr"/>
+      <c r="I35" s="30" t="inlineStr"/>
+      <c r="J35" s="30" t="inlineStr"/>
+      <c r="K35" s="30" t="inlineStr"/>
+      <c r="L35" s="30" t="inlineStr"/>
+      <c r="M35" s="10">
         <f>IF(AND(A35="",B35="",C35="",E35="",F35=""),"",IF(OR(A35="",B35="",C35="",E35="",F35=""),"✗ Required missing",IF(ISNUMBER(VALUE(F35)),IF(VALUE(F35)&lt;=0,"✗ qty&gt;0 required","✓ Valid"),"✗ target_qty not numeric")))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>LIVE SUMMARY (auto-calculates as you add target rows)</t>
         </is>
       </c>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="24" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
-      <c r="I36" s="24" t="n"/>
-      <c r="J36" s="24" t="n"/>
-      <c r="K36" s="24" t="n"/>
-      <c r="L36" s="24" t="n"/>
-      <c r="M36" s="16" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Rows entered</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Valid rows</t>
         </is>
       </c>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Rows with issues</t>
         </is>
       </c>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Total target_qty</t>
         </is>
       </c>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="H37" s="23" t="n"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Total target_nsv</t>
         </is>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Months covered</t>
         </is>
       </c>
-      <c r="L37" s="16" t="n"/>
+      <c r="L37" s="23" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="17">
+      <c r="A38" s="24">
         <f>COUNTA(A6:A35)</f>
         <v/>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="17">
+      <c r="B38" s="23" t="n"/>
+      <c r="C38" s="24">
         <f>COUNTIF(M6:M35,"✓ Valid")</f>
         <v/>
       </c>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="17">
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="24">
         <f>COUNTA(M6:M35)-COUNTIF(M6:M35,"✓ Valid")-COUNTBLANK(M6:M35)</f>
         <v/>
       </c>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="17">
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="24">
         <f>IFERROR(SUM(F6:F35),0)</f>
         <v/>
       </c>
-      <c r="H38" s="16" t="n"/>
-      <c r="I38" s="17">
+      <c r="H38" s="23" t="n"/>
+      <c r="I38" s="24">
         <f>IFERROR(SUM(G6:G35),0)</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="17">
+      <c r="J38" s="23" t="n"/>
+      <c r="K38" s="24">
         <f>IFERROR(SUMPRODUCT(1/COUNTIF(A6:A35,A6:A35)*(A6:A35&lt;&gt;"")),0)</f>
         <v/>
       </c>
-      <c r="L38" s="16" t="n"/>
+      <c r="L38" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3680,112 +3616,112 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>NPI LAUNCH PLAN — Aug–Oct 2026 only  |  Only APPROVED rows affect forecast</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Month 1 = initial fill + launch demand. Month 2 = distribution expansion. Month 3 = normalized run rate. After ramp-up, engine switches to trend-based. Yellow = required. Only APPROVED rows affect production.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>launch_month
 (YYYY-MM)</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>chain_name
 (or ALL)</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>ean</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>launch_type
 (NATIONAL/REGIONAL/CHAIN_EXCLUSIVE)</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>planned_stores</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>expected_distribution_pct
 (%)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>initial_fill_qty</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>monthly_run_rate_qty</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>ramp_up_months
 (1-3)</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>month_1_uplift_pct</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>month_2_uplift_pct</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>month_3_uplift_pct</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>approval_status
 ◀ APPROVED / PENDING</t>
         </is>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>VALIDATION
 (formula)</t>
@@ -3793,540 +3729,523 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>↓  EXAMPLE ROW — delete before uploading  ↓</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Mamaearth</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>New Vitamin C Serum 30ml</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>8906087799999</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>NATIONAL</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>850</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="K5" s="20" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="M5" s="20" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="N5" s="20" t="inlineStr">
+      <c r="N5" s="27" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="O5" s="20" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t>Category Mgr</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr">
+      <c r="P5" s="26" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q5" s="20" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t>Awaiting trade plan</t>
         </is>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="12">
         <f>IF(OR(A5="",E5="",H5="",I5=""),"✗ Required missing",IF(P5="APPROVED","✓ APPROVED",IF(AND(H5&lt;&gt;"",I5&lt;&gt;""),"Ready — set col P = APPROVED","⚠ Complete required fields")))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="21" t="inlineStr"/>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="22" t="inlineStr"/>
-      <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
-      <c r="J6" s="22" t="inlineStr"/>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
-      <c r="O6" s="22" t="inlineStr"/>
-      <c r="P6" s="21" t="inlineStr"/>
-      <c r="Q6" s="22" t="inlineStr"/>
-      <c r="R6" s="10">
+      <c r="A6" s="28" t="inlineStr"/>
+      <c r="B6" s="28" t="inlineStr"/>
+      <c r="C6" s="29" t="inlineStr"/>
+      <c r="D6" s="29" t="inlineStr"/>
+      <c r="E6" s="28" t="inlineStr"/>
+      <c r="F6" s="29" t="inlineStr"/>
+      <c r="G6" s="29" t="inlineStr"/>
+      <c r="H6" s="28" t="inlineStr"/>
+      <c r="I6" s="28" t="inlineStr"/>
+      <c r="J6" s="29" t="inlineStr"/>
+      <c r="K6" s="29" t="inlineStr"/>
+      <c r="L6" s="29" t="inlineStr"/>
+      <c r="M6" s="29" t="inlineStr"/>
+      <c r="N6" s="29" t="inlineStr"/>
+      <c r="O6" s="29" t="inlineStr"/>
+      <c r="P6" s="28" t="inlineStr"/>
+      <c r="Q6" s="29" t="inlineStr"/>
+      <c r="R6" s="12">
         <f>IF(AND(A6="",E6="",H6="",I6=""),"",IF(OR(A6="",E6="",H6="",I6=""),"✗ Required missing",IF(P6="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="21" t="inlineStr"/>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="23" t="inlineStr"/>
-      <c r="D7" s="23" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="23" t="inlineStr"/>
-      <c r="G7" s="23" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="23" t="inlineStr"/>
-      <c r="K7" s="23" t="inlineStr"/>
-      <c r="L7" s="23" t="inlineStr"/>
-      <c r="M7" s="23" t="inlineStr"/>
-      <c r="N7" s="23" t="inlineStr"/>
-      <c r="O7" s="23" t="inlineStr"/>
-      <c r="P7" s="21" t="inlineStr"/>
-      <c r="Q7" s="23" t="inlineStr"/>
-      <c r="R7" s="8">
+      <c r="A7" s="28" t="inlineStr"/>
+      <c r="B7" s="28" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
+      <c r="E7" s="28" t="inlineStr"/>
+      <c r="F7" s="30" t="inlineStr"/>
+      <c r="G7" s="30" t="inlineStr"/>
+      <c r="H7" s="28" t="inlineStr"/>
+      <c r="I7" s="28" t="inlineStr"/>
+      <c r="J7" s="30" t="inlineStr"/>
+      <c r="K7" s="30" t="inlineStr"/>
+      <c r="L7" s="30" t="inlineStr"/>
+      <c r="M7" s="30" t="inlineStr"/>
+      <c r="N7" s="30" t="inlineStr"/>
+      <c r="O7" s="30" t="inlineStr"/>
+      <c r="P7" s="28" t="inlineStr"/>
+      <c r="Q7" s="30" t="inlineStr"/>
+      <c r="R7" s="10">
         <f>IF(AND(A7="",E7="",H7="",I7=""),"",IF(OR(A7="",E7="",H7="",I7=""),"✗ Required missing",IF(P7="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="21" t="inlineStr"/>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="22" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
-      <c r="F8" s="22" t="inlineStr"/>
-      <c r="G8" s="22" t="inlineStr"/>
-      <c r="H8" s="21" t="inlineStr"/>
-      <c r="I8" s="21" t="inlineStr"/>
-      <c r="J8" s="22" t="inlineStr"/>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="22" t="inlineStr"/>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
-      <c r="O8" s="22" t="inlineStr"/>
-      <c r="P8" s="21" t="inlineStr"/>
-      <c r="Q8" s="22" t="inlineStr"/>
-      <c r="R8" s="10">
+      <c r="A8" s="28" t="inlineStr"/>
+      <c r="B8" s="28" t="inlineStr"/>
+      <c r="C8" s="29" t="inlineStr"/>
+      <c r="D8" s="29" t="inlineStr"/>
+      <c r="E8" s="28" t="inlineStr"/>
+      <c r="F8" s="29" t="inlineStr"/>
+      <c r="G8" s="29" t="inlineStr"/>
+      <c r="H8" s="28" t="inlineStr"/>
+      <c r="I8" s="28" t="inlineStr"/>
+      <c r="J8" s="29" t="inlineStr"/>
+      <c r="K8" s="29" t="inlineStr"/>
+      <c r="L8" s="29" t="inlineStr"/>
+      <c r="M8" s="29" t="inlineStr"/>
+      <c r="N8" s="29" t="inlineStr"/>
+      <c r="O8" s="29" t="inlineStr"/>
+      <c r="P8" s="28" t="inlineStr"/>
+      <c r="Q8" s="29" t="inlineStr"/>
+      <c r="R8" s="12">
         <f>IF(AND(A8="",E8="",H8="",I8=""),"",IF(OR(A8="",E8="",H8="",I8=""),"✗ Required missing",IF(P8="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="21" t="inlineStr"/>
-      <c r="B9" s="21" t="inlineStr"/>
-      <c r="C9" s="23" t="inlineStr"/>
-      <c r="D9" s="23" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr"/>
-      <c r="F9" s="23" t="inlineStr"/>
-      <c r="G9" s="23" t="inlineStr"/>
-      <c r="H9" s="21" t="inlineStr"/>
-      <c r="I9" s="21" t="inlineStr"/>
-      <c r="J9" s="23" t="inlineStr"/>
-      <c r="K9" s="23" t="inlineStr"/>
-      <c r="L9" s="23" t="inlineStr"/>
-      <c r="M9" s="23" t="inlineStr"/>
-      <c r="N9" s="23" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr"/>
-      <c r="P9" s="21" t="inlineStr"/>
-      <c r="Q9" s="23" t="inlineStr"/>
-      <c r="R9" s="8">
+      <c r="A9" s="28" t="inlineStr"/>
+      <c r="B9" s="28" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr"/>
+      <c r="E9" s="28" t="inlineStr"/>
+      <c r="F9" s="30" t="inlineStr"/>
+      <c r="G9" s="30" t="inlineStr"/>
+      <c r="H9" s="28" t="inlineStr"/>
+      <c r="I9" s="28" t="inlineStr"/>
+      <c r="J9" s="30" t="inlineStr"/>
+      <c r="K9" s="30" t="inlineStr"/>
+      <c r="L9" s="30" t="inlineStr"/>
+      <c r="M9" s="30" t="inlineStr"/>
+      <c r="N9" s="30" t="inlineStr"/>
+      <c r="O9" s="30" t="inlineStr"/>
+      <c r="P9" s="28" t="inlineStr"/>
+      <c r="Q9" s="30" t="inlineStr"/>
+      <c r="R9" s="10">
         <f>IF(AND(A9="",E9="",H9="",I9=""),"",IF(OR(A9="",E9="",H9="",I9=""),"✗ Required missing",IF(P9="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="21" t="inlineStr"/>
-      <c r="B10" s="21" t="inlineStr"/>
-      <c r="C10" s="22" t="inlineStr"/>
-      <c r="D10" s="22" t="inlineStr"/>
-      <c r="E10" s="21" t="inlineStr"/>
-      <c r="F10" s="22" t="inlineStr"/>
-      <c r="G10" s="22" t="inlineStr"/>
-      <c r="H10" s="21" t="inlineStr"/>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="22" t="inlineStr"/>
-      <c r="K10" s="22" t="inlineStr"/>
-      <c r="L10" s="22" t="inlineStr"/>
-      <c r="M10" s="22" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr"/>
-      <c r="O10" s="22" t="inlineStr"/>
-      <c r="P10" s="21" t="inlineStr"/>
-      <c r="Q10" s="22" t="inlineStr"/>
-      <c r="R10" s="10">
+      <c r="A10" s="28" t="inlineStr"/>
+      <c r="B10" s="28" t="inlineStr"/>
+      <c r="C10" s="29" t="inlineStr"/>
+      <c r="D10" s="29" t="inlineStr"/>
+      <c r="E10" s="28" t="inlineStr"/>
+      <c r="F10" s="29" t="inlineStr"/>
+      <c r="G10" s="29" t="inlineStr"/>
+      <c r="H10" s="28" t="inlineStr"/>
+      <c r="I10" s="28" t="inlineStr"/>
+      <c r="J10" s="29" t="inlineStr"/>
+      <c r="K10" s="29" t="inlineStr"/>
+      <c r="L10" s="29" t="inlineStr"/>
+      <c r="M10" s="29" t="inlineStr"/>
+      <c r="N10" s="29" t="inlineStr"/>
+      <c r="O10" s="29" t="inlineStr"/>
+      <c r="P10" s="28" t="inlineStr"/>
+      <c r="Q10" s="29" t="inlineStr"/>
+      <c r="R10" s="12">
         <f>IF(AND(A10="",E10="",H10="",I10=""),"",IF(OR(A10="",E10="",H10="",I10=""),"✗ Required missing",IF(P10="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="21" t="inlineStr"/>
-      <c r="B11" s="21" t="inlineStr"/>
-      <c r="C11" s="23" t="inlineStr"/>
-      <c r="D11" s="23" t="inlineStr"/>
-      <c r="E11" s="21" t="inlineStr"/>
-      <c r="F11" s="23" t="inlineStr"/>
-      <c r="G11" s="23" t="inlineStr"/>
-      <c r="H11" s="21" t="inlineStr"/>
-      <c r="I11" s="21" t="inlineStr"/>
-      <c r="J11" s="23" t="inlineStr"/>
-      <c r="K11" s="23" t="inlineStr"/>
-      <c r="L11" s="23" t="inlineStr"/>
-      <c r="M11" s="23" t="inlineStr"/>
-      <c r="N11" s="23" t="inlineStr"/>
-      <c r="O11" s="23" t="inlineStr"/>
-      <c r="P11" s="21" t="inlineStr"/>
-      <c r="Q11" s="23" t="inlineStr"/>
-      <c r="R11" s="8">
+      <c r="A11" s="28" t="inlineStr"/>
+      <c r="B11" s="28" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
+      <c r="E11" s="28" t="inlineStr"/>
+      <c r="F11" s="30" t="inlineStr"/>
+      <c r="G11" s="30" t="inlineStr"/>
+      <c r="H11" s="28" t="inlineStr"/>
+      <c r="I11" s="28" t="inlineStr"/>
+      <c r="J11" s="30" t="inlineStr"/>
+      <c r="K11" s="30" t="inlineStr"/>
+      <c r="L11" s="30" t="inlineStr"/>
+      <c r="M11" s="30" t="inlineStr"/>
+      <c r="N11" s="30" t="inlineStr"/>
+      <c r="O11" s="30" t="inlineStr"/>
+      <c r="P11" s="28" t="inlineStr"/>
+      <c r="Q11" s="30" t="inlineStr"/>
+      <c r="R11" s="10">
         <f>IF(AND(A11="",E11="",H11="",I11=""),"",IF(OR(A11="",E11="",H11="",I11=""),"✗ Required missing",IF(P11="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="21" t="inlineStr"/>
-      <c r="B12" s="21" t="inlineStr"/>
-      <c r="C12" s="22" t="inlineStr"/>
-      <c r="D12" s="22" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr"/>
-      <c r="F12" s="22" t="inlineStr"/>
-      <c r="G12" s="22" t="inlineStr"/>
-      <c r="H12" s="21" t="inlineStr"/>
-      <c r="I12" s="21" t="inlineStr"/>
-      <c r="J12" s="22" t="inlineStr"/>
-      <c r="K12" s="22" t="inlineStr"/>
-      <c r="L12" s="22" t="inlineStr"/>
-      <c r="M12" s="22" t="inlineStr"/>
-      <c r="N12" s="22" t="inlineStr"/>
-      <c r="O12" s="22" t="inlineStr"/>
-      <c r="P12" s="21" t="inlineStr"/>
-      <c r="Q12" s="22" t="inlineStr"/>
-      <c r="R12" s="10">
+      <c r="A12" s="28" t="inlineStr"/>
+      <c r="B12" s="28" t="inlineStr"/>
+      <c r="C12" s="29" t="inlineStr"/>
+      <c r="D12" s="29" t="inlineStr"/>
+      <c r="E12" s="28" t="inlineStr"/>
+      <c r="F12" s="29" t="inlineStr"/>
+      <c r="G12" s="29" t="inlineStr"/>
+      <c r="H12" s="28" t="inlineStr"/>
+      <c r="I12" s="28" t="inlineStr"/>
+      <c r="J12" s="29" t="inlineStr"/>
+      <c r="K12" s="29" t="inlineStr"/>
+      <c r="L12" s="29" t="inlineStr"/>
+      <c r="M12" s="29" t="inlineStr"/>
+      <c r="N12" s="29" t="inlineStr"/>
+      <c r="O12" s="29" t="inlineStr"/>
+      <c r="P12" s="28" t="inlineStr"/>
+      <c r="Q12" s="29" t="inlineStr"/>
+      <c r="R12" s="12">
         <f>IF(AND(A12="",E12="",H12="",I12=""),"",IF(OR(A12="",E12="",H12="",I12=""),"✗ Required missing",IF(P12="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="21" t="inlineStr"/>
-      <c r="B13" s="21" t="inlineStr"/>
-      <c r="C13" s="23" t="inlineStr"/>
-      <c r="D13" s="23" t="inlineStr"/>
-      <c r="E13" s="21" t="inlineStr"/>
-      <c r="F13" s="23" t="inlineStr"/>
-      <c r="G13" s="23" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr"/>
-      <c r="I13" s="21" t="inlineStr"/>
-      <c r="J13" s="23" t="inlineStr"/>
-      <c r="K13" s="23" t="inlineStr"/>
-      <c r="L13" s="23" t="inlineStr"/>
-      <c r="M13" s="23" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr"/>
-      <c r="O13" s="23" t="inlineStr"/>
-      <c r="P13" s="21" t="inlineStr"/>
-      <c r="Q13" s="23" t="inlineStr"/>
-      <c r="R13" s="8">
+      <c r="A13" s="28" t="inlineStr"/>
+      <c r="B13" s="28" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr"/>
+      <c r="E13" s="28" t="inlineStr"/>
+      <c r="F13" s="30" t="inlineStr"/>
+      <c r="G13" s="30" t="inlineStr"/>
+      <c r="H13" s="28" t="inlineStr"/>
+      <c r="I13" s="28" t="inlineStr"/>
+      <c r="J13" s="30" t="inlineStr"/>
+      <c r="K13" s="30" t="inlineStr"/>
+      <c r="L13" s="30" t="inlineStr"/>
+      <c r="M13" s="30" t="inlineStr"/>
+      <c r="N13" s="30" t="inlineStr"/>
+      <c r="O13" s="30" t="inlineStr"/>
+      <c r="P13" s="28" t="inlineStr"/>
+      <c r="Q13" s="30" t="inlineStr"/>
+      <c r="R13" s="10">
         <f>IF(AND(A13="",E13="",H13="",I13=""),"",IF(OR(A13="",E13="",H13="",I13=""),"✗ Required missing",IF(P13="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="21" t="inlineStr"/>
-      <c r="B14" s="21" t="inlineStr"/>
-      <c r="C14" s="22" t="inlineStr"/>
-      <c r="D14" s="22" t="inlineStr"/>
-      <c r="E14" s="21" t="inlineStr"/>
-      <c r="F14" s="22" t="inlineStr"/>
-      <c r="G14" s="22" t="inlineStr"/>
-      <c r="H14" s="21" t="inlineStr"/>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="22" t="inlineStr"/>
-      <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="22" t="inlineStr"/>
-      <c r="M14" s="22" t="inlineStr"/>
-      <c r="N14" s="22" t="inlineStr"/>
-      <c r="O14" s="22" t="inlineStr"/>
-      <c r="P14" s="21" t="inlineStr"/>
-      <c r="Q14" s="22" t="inlineStr"/>
-      <c r="R14" s="10">
+      <c r="A14" s="28" t="inlineStr"/>
+      <c r="B14" s="28" t="inlineStr"/>
+      <c r="C14" s="29" t="inlineStr"/>
+      <c r="D14" s="29" t="inlineStr"/>
+      <c r="E14" s="28" t="inlineStr"/>
+      <c r="F14" s="29" t="inlineStr"/>
+      <c r="G14" s="29" t="inlineStr"/>
+      <c r="H14" s="28" t="inlineStr"/>
+      <c r="I14" s="28" t="inlineStr"/>
+      <c r="J14" s="29" t="inlineStr"/>
+      <c r="K14" s="29" t="inlineStr"/>
+      <c r="L14" s="29" t="inlineStr"/>
+      <c r="M14" s="29" t="inlineStr"/>
+      <c r="N14" s="29" t="inlineStr"/>
+      <c r="O14" s="29" t="inlineStr"/>
+      <c r="P14" s="28" t="inlineStr"/>
+      <c r="Q14" s="29" t="inlineStr"/>
+      <c r="R14" s="12">
         <f>IF(AND(A14="",E14="",H14="",I14=""),"",IF(OR(A14="",E14="",H14="",I14=""),"✗ Required missing",IF(P14="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="21" t="inlineStr"/>
-      <c r="B15" s="21" t="inlineStr"/>
-      <c r="C15" s="23" t="inlineStr"/>
-      <c r="D15" s="23" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr"/>
-      <c r="F15" s="23" t="inlineStr"/>
-      <c r="G15" s="23" t="inlineStr"/>
-      <c r="H15" s="21" t="inlineStr"/>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="23" t="inlineStr"/>
-      <c r="K15" s="23" t="inlineStr"/>
-      <c r="L15" s="23" t="inlineStr"/>
-      <c r="M15" s="23" t="inlineStr"/>
-      <c r="N15" s="23" t="inlineStr"/>
-      <c r="O15" s="23" t="inlineStr"/>
-      <c r="P15" s="21" t="inlineStr"/>
-      <c r="Q15" s="23" t="inlineStr"/>
-      <c r="R15" s="8">
+      <c r="A15" s="28" t="inlineStr"/>
+      <c r="B15" s="28" t="inlineStr"/>
+      <c r="C15" s="30" t="inlineStr"/>
+      <c r="D15" s="30" t="inlineStr"/>
+      <c r="E15" s="28" t="inlineStr"/>
+      <c r="F15" s="30" t="inlineStr"/>
+      <c r="G15" s="30" t="inlineStr"/>
+      <c r="H15" s="28" t="inlineStr"/>
+      <c r="I15" s="28" t="inlineStr"/>
+      <c r="J15" s="30" t="inlineStr"/>
+      <c r="K15" s="30" t="inlineStr"/>
+      <c r="L15" s="30" t="inlineStr"/>
+      <c r="M15" s="30" t="inlineStr"/>
+      <c r="N15" s="30" t="inlineStr"/>
+      <c r="O15" s="30" t="inlineStr"/>
+      <c r="P15" s="28" t="inlineStr"/>
+      <c r="Q15" s="30" t="inlineStr"/>
+      <c r="R15" s="10">
         <f>IF(AND(A15="",E15="",H15="",I15=""),"",IF(OR(A15="",E15="",H15="",I15=""),"✗ Required missing",IF(P15="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="21" t="inlineStr"/>
-      <c r="B16" s="21" t="inlineStr"/>
-      <c r="C16" s="22" t="inlineStr"/>
-      <c r="D16" s="22" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr"/>
-      <c r="F16" s="22" t="inlineStr"/>
-      <c r="G16" s="22" t="inlineStr"/>
-      <c r="H16" s="21" t="inlineStr"/>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="22" t="inlineStr"/>
-      <c r="K16" s="22" t="inlineStr"/>
-      <c r="L16" s="22" t="inlineStr"/>
-      <c r="M16" s="22" t="inlineStr"/>
-      <c r="N16" s="22" t="inlineStr"/>
-      <c r="O16" s="22" t="inlineStr"/>
-      <c r="P16" s="21" t="inlineStr"/>
-      <c r="Q16" s="22" t="inlineStr"/>
-      <c r="R16" s="10">
+      <c r="A16" s="28" t="inlineStr"/>
+      <c r="B16" s="28" t="inlineStr"/>
+      <c r="C16" s="29" t="inlineStr"/>
+      <c r="D16" s="29" t="inlineStr"/>
+      <c r="E16" s="28" t="inlineStr"/>
+      <c r="F16" s="29" t="inlineStr"/>
+      <c r="G16" s="29" t="inlineStr"/>
+      <c r="H16" s="28" t="inlineStr"/>
+      <c r="I16" s="28" t="inlineStr"/>
+      <c r="J16" s="29" t="inlineStr"/>
+      <c r="K16" s="29" t="inlineStr"/>
+      <c r="L16" s="29" t="inlineStr"/>
+      <c r="M16" s="29" t="inlineStr"/>
+      <c r="N16" s="29" t="inlineStr"/>
+      <c r="O16" s="29" t="inlineStr"/>
+      <c r="P16" s="28" t="inlineStr"/>
+      <c r="Q16" s="29" t="inlineStr"/>
+      <c r="R16" s="12">
         <f>IF(AND(A16="",E16="",H16="",I16=""),"",IF(OR(A16="",E16="",H16="",I16=""),"✗ Required missing",IF(P16="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="21" t="inlineStr"/>
-      <c r="B17" s="21" t="inlineStr"/>
-      <c r="C17" s="23" t="inlineStr"/>
-      <c r="D17" s="23" t="inlineStr"/>
-      <c r="E17" s="21" t="inlineStr"/>
-      <c r="F17" s="23" t="inlineStr"/>
-      <c r="G17" s="23" t="inlineStr"/>
-      <c r="H17" s="21" t="inlineStr"/>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="23" t="inlineStr"/>
-      <c r="K17" s="23" t="inlineStr"/>
-      <c r="L17" s="23" t="inlineStr"/>
-      <c r="M17" s="23" t="inlineStr"/>
-      <c r="N17" s="23" t="inlineStr"/>
-      <c r="O17" s="23" t="inlineStr"/>
-      <c r="P17" s="21" t="inlineStr"/>
-      <c r="Q17" s="23" t="inlineStr"/>
-      <c r="R17" s="8">
+      <c r="A17" s="28" t="inlineStr"/>
+      <c r="B17" s="28" t="inlineStr"/>
+      <c r="C17" s="30" t="inlineStr"/>
+      <c r="D17" s="30" t="inlineStr"/>
+      <c r="E17" s="28" t="inlineStr"/>
+      <c r="F17" s="30" t="inlineStr"/>
+      <c r="G17" s="30" t="inlineStr"/>
+      <c r="H17" s="28" t="inlineStr"/>
+      <c r="I17" s="28" t="inlineStr"/>
+      <c r="J17" s="30" t="inlineStr"/>
+      <c r="K17" s="30" t="inlineStr"/>
+      <c r="L17" s="30" t="inlineStr"/>
+      <c r="M17" s="30" t="inlineStr"/>
+      <c r="N17" s="30" t="inlineStr"/>
+      <c r="O17" s="30" t="inlineStr"/>
+      <c r="P17" s="28" t="inlineStr"/>
+      <c r="Q17" s="30" t="inlineStr"/>
+      <c r="R17" s="10">
         <f>IF(AND(A17="",E17="",H17="",I17=""),"",IF(OR(A17="",E17="",H17="",I17=""),"✗ Required missing",IF(P17="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="21" t="inlineStr"/>
-      <c r="B18" s="21" t="inlineStr"/>
-      <c r="C18" s="22" t="inlineStr"/>
-      <c r="D18" s="22" t="inlineStr"/>
-      <c r="E18" s="21" t="inlineStr"/>
-      <c r="F18" s="22" t="inlineStr"/>
-      <c r="G18" s="22" t="inlineStr"/>
-      <c r="H18" s="21" t="inlineStr"/>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="22" t="inlineStr"/>
-      <c r="K18" s="22" t="inlineStr"/>
-      <c r="L18" s="22" t="inlineStr"/>
-      <c r="M18" s="22" t="inlineStr"/>
-      <c r="N18" s="22" t="inlineStr"/>
-      <c r="O18" s="22" t="inlineStr"/>
-      <c r="P18" s="21" t="inlineStr"/>
-      <c r="Q18" s="22" t="inlineStr"/>
-      <c r="R18" s="10">
+      <c r="A18" s="28" t="inlineStr"/>
+      <c r="B18" s="28" t="inlineStr"/>
+      <c r="C18" s="29" t="inlineStr"/>
+      <c r="D18" s="29" t="inlineStr"/>
+      <c r="E18" s="28" t="inlineStr"/>
+      <c r="F18" s="29" t="inlineStr"/>
+      <c r="G18" s="29" t="inlineStr"/>
+      <c r="H18" s="28" t="inlineStr"/>
+      <c r="I18" s="28" t="inlineStr"/>
+      <c r="J18" s="29" t="inlineStr"/>
+      <c r="K18" s="29" t="inlineStr"/>
+      <c r="L18" s="29" t="inlineStr"/>
+      <c r="M18" s="29" t="inlineStr"/>
+      <c r="N18" s="29" t="inlineStr"/>
+      <c r="O18" s="29" t="inlineStr"/>
+      <c r="P18" s="28" t="inlineStr"/>
+      <c r="Q18" s="29" t="inlineStr"/>
+      <c r="R18" s="12">
         <f>IF(AND(A18="",E18="",H18="",I18=""),"",IF(OR(A18="",E18="",H18="",I18=""),"✗ Required missing",IF(P18="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="21" t="inlineStr"/>
-      <c r="B19" s="21" t="inlineStr"/>
-      <c r="C19" s="23" t="inlineStr"/>
-      <c r="D19" s="23" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr"/>
-      <c r="F19" s="23" t="inlineStr"/>
-      <c r="G19" s="23" t="inlineStr"/>
-      <c r="H19" s="21" t="inlineStr"/>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="23" t="inlineStr"/>
-      <c r="K19" s="23" t="inlineStr"/>
-      <c r="L19" s="23" t="inlineStr"/>
-      <c r="M19" s="23" t="inlineStr"/>
-      <c r="N19" s="23" t="inlineStr"/>
-      <c r="O19" s="23" t="inlineStr"/>
-      <c r="P19" s="21" t="inlineStr"/>
-      <c r="Q19" s="23" t="inlineStr"/>
-      <c r="R19" s="8">
+      <c r="A19" s="28" t="inlineStr"/>
+      <c r="B19" s="28" t="inlineStr"/>
+      <c r="C19" s="30" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
+      <c r="E19" s="28" t="inlineStr"/>
+      <c r="F19" s="30" t="inlineStr"/>
+      <c r="G19" s="30" t="inlineStr"/>
+      <c r="H19" s="28" t="inlineStr"/>
+      <c r="I19" s="28" t="inlineStr"/>
+      <c r="J19" s="30" t="inlineStr"/>
+      <c r="K19" s="30" t="inlineStr"/>
+      <c r="L19" s="30" t="inlineStr"/>
+      <c r="M19" s="30" t="inlineStr"/>
+      <c r="N19" s="30" t="inlineStr"/>
+      <c r="O19" s="30" t="inlineStr"/>
+      <c r="P19" s="28" t="inlineStr"/>
+      <c r="Q19" s="30" t="inlineStr"/>
+      <c r="R19" s="10">
         <f>IF(AND(A19="",E19="",H19="",I19=""),"",IF(OR(A19="",E19="",H19="",I19=""),"✗ Required missing",IF(P19="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="21" t="inlineStr"/>
-      <c r="B20" s="21" t="inlineStr"/>
-      <c r="C20" s="22" t="inlineStr"/>
-      <c r="D20" s="22" t="inlineStr"/>
-      <c r="E20" s="21" t="inlineStr"/>
-      <c r="F20" s="22" t="inlineStr"/>
-      <c r="G20" s="22" t="inlineStr"/>
-      <c r="H20" s="21" t="inlineStr"/>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="22" t="inlineStr"/>
-      <c r="K20" s="22" t="inlineStr"/>
-      <c r="L20" s="22" t="inlineStr"/>
-      <c r="M20" s="22" t="inlineStr"/>
-      <c r="N20" s="22" t="inlineStr"/>
-      <c r="O20" s="22" t="inlineStr"/>
-      <c r="P20" s="21" t="inlineStr"/>
-      <c r="Q20" s="22" t="inlineStr"/>
-      <c r="R20" s="10">
+      <c r="A20" s="28" t="inlineStr"/>
+      <c r="B20" s="28" t="inlineStr"/>
+      <c r="C20" s="29" t="inlineStr"/>
+      <c r="D20" s="29" t="inlineStr"/>
+      <c r="E20" s="28" t="inlineStr"/>
+      <c r="F20" s="29" t="inlineStr"/>
+      <c r="G20" s="29" t="inlineStr"/>
+      <c r="H20" s="28" t="inlineStr"/>
+      <c r="I20" s="28" t="inlineStr"/>
+      <c r="J20" s="29" t="inlineStr"/>
+      <c r="K20" s="29" t="inlineStr"/>
+      <c r="L20" s="29" t="inlineStr"/>
+      <c r="M20" s="29" t="inlineStr"/>
+      <c r="N20" s="29" t="inlineStr"/>
+      <c r="O20" s="29" t="inlineStr"/>
+      <c r="P20" s="28" t="inlineStr"/>
+      <c r="Q20" s="29" t="inlineStr"/>
+      <c r="R20" s="12">
         <f>IF(AND(A20="",E20="",H20="",I20=""),"",IF(OR(A20="",E20="",H20="",I20=""),"✗ Required missing",IF(P20="APPROVED","✓ APPROVED","Set col P = APPROVED")))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>LIVE NPI SUMMARY</t>
         </is>
       </c>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="24" t="n"/>
-      <c r="H22" s="24" t="n"/>
-      <c r="I22" s="24" t="n"/>
-      <c r="J22" s="24" t="n"/>
-      <c r="K22" s="24" t="n"/>
-      <c r="L22" s="24" t="n"/>
-      <c r="M22" s="24" t="n"/>
-      <c r="N22" s="24" t="n"/>
-      <c r="O22" s="24" t="n"/>
-      <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="24" t="n"/>
-      <c r="R22" s="16" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>NPIs entered</t>
         </is>
       </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H23" s="24" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="H23" s="31" t="n"/>
+      <c r="I23" s="23" t="n"/>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Total initial fill</t>
         </is>
       </c>
-      <c r="K23" s="24" t="n"/>
-      <c r="L23" s="16" t="n"/>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="K23" s="31" t="n"/>
+      <c r="L23" s="23" t="n"/>
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>Approval rate</t>
         </is>
       </c>
-      <c r="N23" s="24" t="n"/>
-      <c r="O23" s="16" t="n"/>
+      <c r="N23" s="31" t="n"/>
+      <c r="O23" s="23" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="17">
+      <c r="A24" s="24">
         <f>COUNTA(A6:A20)</f>
         <v/>
       </c>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="17">
+      <c r="B24" s="31" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="24">
         <f>COUNTIF(P6:P20,"APPROVED")</f>
         <v/>
       </c>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="17">
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="24">
         <f>COUNTA(P6:P20)-COUNTIF(P6:P20,"APPROVED")</f>
         <v/>
       </c>
-      <c r="H24" s="24" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="17">
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="24">
         <f>IFERROR(SUM(I6:I20),0)</f>
         <v/>
       </c>
-      <c r="K24" s="24" t="n"/>
-      <c r="L24" s="16" t="n"/>
-      <c r="M24" s="25">
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="23" t="n"/>
+      <c r="M24" s="32">
         <f>IFERROR(COUNTIF(P6:P20,"APPROVED")/COUNTA(P6:P20),0)</f>
         <v/>
       </c>
-      <c r="N24" s="24" t="n"/>
-      <c r="O24" s="16" t="n"/>
+      <c r="N24" s="31" t="n"/>
+      <c r="O24" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4339,9 +4258,9 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G23:I23"/>
     <mergeCell ref="J23:L23"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="M24:O24"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A22:R22"/>
     <mergeCell ref="A4:R4"/>
   </mergeCells>
@@ -4358,534 +4277,491 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>MARGIN REPOSITORY STATUS  |  CM2 reporting BLOCKED until Finance sets approval_status = FINANCE_APPROVED</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>DERIVED = computed from offtake (directional, not Finance-approved).  ESTIMATED = placeholder MRP ₹250, margin 30%, cm2 15% — must be replaced with real Finance data.  Negative margin_pct = data quality issue — must be resolved before CM2 reporting.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>quality_status</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>count_rows</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>count_eans</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>count_chains</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>avg_mrp (₹)</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>avg_margin_pct (%)</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>avg_cm2_pct (%)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>negative_margin_rows</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>approval_status_required</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="B4" s="23" t="n">
+      <c r="B4" s="30" t="n">
         <v>2113</v>
       </c>
-      <c r="C4" s="23" t="n">
+      <c r="C4" s="30" t="n">
         <v>507</v>
       </c>
-      <c r="D4" s="23" t="n">
+      <c r="D4" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>₹21597</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>44.2%</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>2591.6%</t>
         </is>
       </c>
-      <c r="H4" s="27" t="n">
+      <c r="H4" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>FINANCE_APPROVED required</t>
         </is>
       </c>
-      <c r="J4" s="23" t="inlineStr">
+      <c r="J4" s="30" t="inlineStr">
         <is>
           <t>Finance Controller</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>ESTIMATED</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="29" t="n">
         <v>933</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="29" t="n">
         <v>933</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>₹250 (PLACEHOLDER)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>REPLACE WITH REAL DATA — BLOCKED</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="29" t="inlineStr">
         <is>
           <t>Finance + Category</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>DATA QUALITY ISSUES — must resolve before Finance sign-off</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n"/>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="24" t="n"/>
-      <c r="H7" s="24" t="n"/>
-      <c r="I7" s="24" t="n"/>
-      <c r="J7" s="16" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>ean</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>chain</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>mrp</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>margin_pct</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>issue_type</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>recommended_action</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>8904417314298</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>VMM</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Mamaearth</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Rice Dewy Bright Face Wash</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>750</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>−84.64</t>
         </is>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" s="35" t="inlineStr">
         <is>
           <t>NEGATIVE_MARGIN</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Reclassify as return/credit memo or exclude from master</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Re-derive using aggregate NSV (see root cause below)</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>MDM / Finance</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>8904417312546</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>VMM</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Mamaearth</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Vitamin C Face Wash 150 ml</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>562.5</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>−84.64</t>
         </is>
       </c>
-      <c r="H10" s="28" t="inlineStr">
+      <c r="H10" s="35" t="inlineStr">
         <is>
           <t>NEGATIVE_MARGIN</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Reclassify as return/credit memo or exclude from master</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>Re-derive using aggregate NSV (see root cause below)</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>MDM / Finance</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ROOT CAUSE ANALYSIS — VMM negative margin_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>action_required</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Mixed denomination</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>VMM MRP = ₹750 / ₹562.5 (per-unit values). Other chains show ₹2,245–₹80,820 (aggregate NSV). Data pipeline used per-unit MRP but aggregate-denominated margin computation → wrong sign on margin_pct.</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Re-derive VMM rows: confirm whether source is per-unit or aggregate; re-run margin ETL with consistent denomination.</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Internal inconsistency</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>cm2_pct = +90 / +67.5 (positive) while margin_pct = −84.64% (negative) for the same rows. Mathematically inconsistent — one of the two computed columns used incorrect inputs.</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>After denomination fix, verify that margin_pct &gt; 0 and cm2_pct &gt; 0 before setting approval_status = FINANCE_APPROVED.</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Tentative treatment</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>In TENTATIVE mode, VMM chain is excluded from the forecast (value_source = EXCLUDED_VMM). Chain × EAN rows for VMM will show confidence_level = EXCLUDED in tentative forecast outputs.</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Resolve root cause, then re-run in FINAL mode with corrected VMM margins.</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>TENTATIVE_WORKAROUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>REQUIRED FULL MARGIN SCHEMA — provide to Finance for export</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>column_name</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>format</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>current_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>YYYY-MM</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Present (DERIVED/ESTIMATED)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>chain_name</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>ean</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>mrp</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>₹ per unit</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Present — ESTIMATED rows = ₹250 placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>gst_pct</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>invoice_discount_pct</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+          <t>YYYY-MM</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>REQUIRED</t>
         </is>
@@ -4895,51 +4771,51 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Present (DERIVED/ESTIMATED)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>off_invoice_discount_pct</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>chain_name</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>REQUIRED</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Present</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>tot_pct</t>
+          <t>ean</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>REQUIRED</t>
         </is>
@@ -4951,49 +4827,49 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Present (as tot_pct)</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>trade_margin_pct</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>mrp</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>₹ per unit</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>REQUIRED</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Present as margin_pct — name mismatch</t>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Present — ESTIMATED rows = ₹250 placeholder</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>cogs_per_unit</t>
+          <t>gst_pct</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>₹</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>REQUIRED</t>
         </is>
@@ -5003,34 +4879,34 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>claim_per_unit</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>₹</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>invoice_discount_pct</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -5039,17 +4915,17 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>ba_cost_per_unit</t>
+          <t>off_invoice_discount_pct</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>₹</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -5057,88 +4933,88 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>visibility_cost_per_unit</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>₹</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>tot_pct</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Present (as tot_pct)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>rental_cost_per_unit</t>
+          <t>trade_margin_pct</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Present as margin_pct — name mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>cogs_per_unit</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
           <t>₹</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>cm1_pct</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -5147,17 +5023,17 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>cm2_pct</t>
+          <t>claim_per_unit</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>₹</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>REQUIRED</t>
+          <t>OPTIONAL</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -5165,34 +5041,34 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Present — ESTIMATED rows = 15% placeholder</t>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>approval_status</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>FINANCE_APPROVED / PROVISIONAL</t>
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>ba_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>₹</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Finance Controller</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
+          <t>OPTIONAL</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -5201,227 +5077,199 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
+          <t>visibility_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>rental_cost_per_unit</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>cm1_pct</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>cm2_pct</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Present — ESTIMATED rows = 15% placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>FINANCE_APPROVED / PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Finance Controller</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
           <t>effective_from</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>REQUIRED</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>effective_to</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>YYYY-MM or OPEN</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>REQUIRED</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="39" t="inlineStr">
-        <is>
-          <t>VMM CHAIN — NEGATIVE MARGIN INVESTIGATION (QC 2026-08-01)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>ean</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>mrp_in_master</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>margin_pct</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>cm2_pct</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>recommended_action</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>8904417314298</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Rice Dewy Bright Face Wash</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>VMM</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>₹750</t>
-        </is>
-      </c>
-      <c r="E37" s="40" t="inlineStr">
-        <is>
-          <t>-84.64%</t>
-        </is>
-      </c>
-      <c r="F37" s="41" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
-      </c>
-      <c r="G37" s="41" t="inlineStr">
-        <is>
-          <t>Internally inconsistent: cm2_pct=90% while margin_pct=-84.64% — impossible for same record. VMM MRP (₹750) is per-unit, other chains show aggregate NSV (₹80,820–₹2,245). Derived computation used wrong unit for VMM — likely mixed up per-unit vs total NSV.</t>
-        </is>
-      </c>
-      <c r="H37" s="41" t="inlineStr">
-        <is>
-          <t>1. Pull raw VMM offtake record for Apr 2026. 2. Verify if VMM MRP=₹750 is per-unit (plausible for 150ml face wash) vs aggregate. 3. Re-derive margin_pct using correct unit denomination. 4. If a credit/return record exists, exclude from margin master.</t>
-        </is>
-      </c>
-      <c r="I37" s="41" t="inlineStr">
-        <is>
-          <t>FY26 primary: 553 rows for these 2 EANs across 23 chains (all positive MRP/qty). VMM is isolated outlier — other chains show 36-68% margin_pct.</t>
-        </is>
-      </c>
-      <c r="J37" s="41" t="inlineStr">
-        <is>
-          <t>MDM / Finance — PRIORITY P1 before V-16 can PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>8904417312546</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Vitamin C Face Wash 150 ml</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>VMM</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>₹562.5</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>-84.64%</t>
-        </is>
-      </c>
-      <c r="F38" s="42" t="inlineStr">
-        <is>
-          <t>67.50</t>
-        </is>
-      </c>
-      <c r="G38" s="42" t="inlineStr">
-        <is>
-          <t>Same issue as EAN 8904417314298. ₹562.5 = plausible per-unit MRP. Margin_pct=-84.64% identical to above — suggests same computation error, not coincidence.</t>
-        </is>
-      </c>
-      <c r="H38" s="42" t="inlineStr">
-        <is>
-          <t>Same as above — verify unit denomination for VMM chain in source offtake data.</t>
-        </is>
-      </c>
-      <c r="I38" s="42" t="inlineStr">
-        <is>
-          <t>Other chains: Apollo ₹1,347, Dmart ₹20,205 (aggregate NSV not per-unit). VMM outlier confirmed.</t>
-        </is>
-      </c>
-      <c r="J38" s="42" t="inlineStr">
-        <is>
-          <t>MDM / Finance — PRIORITY P1 before V-16 can PASS</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5449,314 +5297,305 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>UNMAPPED EAN REGISTER  |  5 EANs in offtake not in margin master — resolve before UAT</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ean</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>article_source_name</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>chain_name</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>months_seen</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>sales_qty</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>sales_nsv</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>issue_type</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>recommended_action</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Run audit — EAN slot 1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr"/>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr"/>
+      <c r="C3" s="10" t="inlineStr"/>
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Apr–May 2026</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr"/>
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>OPEN — PENDING INVESTIGATION</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>Investigate &amp; reclassify</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>MDM / Category</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Run audit — EAN slot 2</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr"/>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr"/>
+      <c r="C4" s="12" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Apr–May 2026</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>OPEN — PENDING INVESTIGATION</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>Investigate &amp; reclassify</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>MDM / Category</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Run audit — EAN slot 3</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr"/>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr"/>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Apr–May 2026</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>OPEN — PENDING INVESTIGATION</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>Investigate &amp; reclassify</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>MDM / Category</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Run audit — EAN slot 4</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr"/>
+      <c r="C6" s="12" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Apr–May 2026</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr"/>
+      <c r="F6" s="12" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>OPEN — PENDING INVESTIGATION</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>Investigate &amp; reclassify</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>MDM / Category</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Run audit — EAN slot 5</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Apr–May 2026</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>OPEN — PENDING INVESTIGATION</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>Investigate &amp; reclassify</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>MDM / Category</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>To populate: python forecast_engine/data_readiness_audit.py  →  copy unmapped_eans from audit_output/audit_issues.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>RESOLUTION PROGRESS</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="16" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Total EANs</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Still Open</t>
         </is>
       </c>
-      <c r="H12" s="16" t="n"/>
+      <c r="H12" s="23" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="30">
+      <c r="A13" s="38">
         <f>COUNTA(A3:A7)</f>
         <v/>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="30">
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="38">
         <f>COUNTIF(J3:J7,"RESOLVED")</f>
         <v/>
       </c>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="30">
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="38">
         <f>COUNTIF(J3:J7,"EXCLUDED")</f>
         <v/>
       </c>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="30">
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="38">
         <f>COUNTIF(J3:J7,"OPEN")</f>
         <v/>
       </c>
-      <c r="H13" s="16" t="n"/>
+      <c r="H13" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5782,7 +5621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5794,1118 +5633,1239 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>PRE-REFRESH VALIDATION CHECKLIST  |  Run: python validate_business_inputs.py --mode full</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED = Stop. Do not run forecast.  FAIL = Fix before running.  WARNING = Document and proceed with caution.  Column H status auto-updates when you paste actual results in col G.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>PRE-REFRESH VALIDATION CHECKLIST  |  FINAL: python validate_business_inputs.py --mode final  |  TENTATIVE: python validate_business_inputs.py --mode tentative</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>FINAL MODE — BLOCKED = Stop. FAIL = Fix before running. WARNING = Document and proceed with caution.  TENTATIVE MODE — Only structural BLOCKED checks stop the run; approval gates downgraded to WARNING.  Column H status auto-updates when you paste actual results in col G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Check ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Check Description</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Severity
+(FINAL)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Validation Rule</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Pass Criterion</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Actual Result
 (paste after running)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Status
 (formula)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Tentative Mode</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>V-01</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>targets.csv</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>At least one data row present</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Row count &gt; 0</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>≥ 1 row for Aug–Oct 2026</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="9">
+      <c r="G4" s="17" t="inlineStr"/>
+      <c r="H4" s="11">
         <f>IF(G4="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G4)),G4="0",G4="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G4)),ISNUMBER(SEARCH("FAIL",G4))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Most critical missing input. Upload Chain × Brand × EAN targets.</t>
         </is>
       </c>
+      <c r="J4" s="39" t="inlineStr">
+        <is>
+          <t>WARNING — uses history-based baseline</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>V-02</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>targets.csv</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>No blanks in required columns</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>No NaN in month, chain_name, brand, ean, target_qty</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>0 blank required fields</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr"/>
-      <c r="H5" s="9">
+      <c r="G5" s="17" t="inlineStr"/>
+      <c r="H5" s="11">
         <f>IF(G5="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G5)),G5="0",G5="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G5)),ISNUMBER(SEARCH("FAIL",G5))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I5" s="10" t="inlineStr"/>
+      <c r="I5" s="12" t="inlineStr"/>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>BLOCKED (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>V-03</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>targets.csv</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>month format YYYY-MM</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>regex \d{4}-\d{2}</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>All rows match</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr"/>
-      <c r="H6" s="9">
+      <c r="G6" s="17" t="inlineStr"/>
+      <c r="H6" s="11">
         <f>IF(G6="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G6)),G6="0",G6="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G6)),ISNUMBER(SEARCH("FAIL",G6))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I6" s="8" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>V-04</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>targets.csv</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>No negative target_qty or target_nsv</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>target_qty &gt;= 0, target_nsv &gt;= 0</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>0 negative values</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr"/>
-      <c r="H7" s="9">
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="11">
         <f>IF(G7="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G7)),G7="0",G7="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G7)),ISNUMBER(SEARCH("FAIL",G7))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I7" s="10" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr"/>
+      <c r="J7" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>V-05</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>targets.csv</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>No duplicate month × chain × brand × ean</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Deduplication check</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>0 duplicates</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr"/>
-      <c r="H8" s="9">
+      <c r="G8" s="17" t="inlineStr"/>
+      <c r="H8" s="11">
         <f>IF(G8="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G8)),G8="0",G8="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G8)),ISNUMBER(SEARCH("FAIL",G8))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I8" s="8" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>BLOCKED (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>V-06</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>targets.csv</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>No MISSING quality_status rows</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>quality_status != MISSING</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>0 MISSING rows</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr"/>
-      <c r="H9" s="9">
+      <c r="G9" s="17" t="inlineStr"/>
+      <c r="H9" s="11">
         <f>IF(G9="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G9)),G9="0",G9="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G9)),ISNUMBER(SEARCH("FAIL",G9))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I9" s="10" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
+      <c r="J9" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>V-07</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>events_calendar.csv</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>No PLACEHOLDER_TBC rows</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>status = APPROVED only</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>0 PLACEHOLDER_TBC rows</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr"/>
-      <c r="H10" s="9">
+      <c r="G10" s="17" t="inlineStr"/>
+      <c r="H10" s="11">
         <f>IF(G10="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G10)),G10="0",G10="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G10)),ISNUMBER(SEARCH("FAIL",G10))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>All 13 events currently PLACEHOLDER_TBC.</t>
         </is>
       </c>
+      <c r="J10" s="39" t="inlineStr">
+        <is>
+          <t>WARNING — uses 0% uplift or Proposed_base_pct from EVENTS_APPROVAL col T</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>V-08</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>events_calendar.csv</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>No overlapping events same chain × brand × month</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>No dup forecast_month + chain + brand</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>0 overlapping rows</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr"/>
-      <c r="H11" s="9">
+      <c r="G11" s="17" t="inlineStr"/>
+      <c r="H11" s="11">
         <f>IF(G11="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G11)),G11="0",G11="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G11)),ISNUMBER(SEARCH("FAIL",G11))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I11" s="10" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
+      <c r="J11" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>V-09</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>events_calendar.csv</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>uplift_pct between 0 and 100</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>0 &lt;= uplift_pct &lt;= 100</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>All rows within range</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr"/>
-      <c r="H12" s="9">
+      <c r="G12" s="17" t="inlineStr"/>
+      <c r="H12" s="11">
         <f>IF(G12="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G12)),G12="0",G12="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G12)),ISNUMBER(SEARCH("FAIL",G12))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I12" s="8" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>V-10</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>events_calendar.csv</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>forecast_month format YYYY-MM</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>regex \d{4}-\d{2}</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>All rows match</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr"/>
-      <c r="H13" s="9">
+      <c r="G13" s="17" t="inlineStr"/>
+      <c r="H13" s="11">
         <f>IF(G13="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G13)),G13="0",G13="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G13)),ISNUMBER(SEARCH("FAIL",G13))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I13" s="10" t="inlineStr"/>
+      <c r="I13" s="12" t="inlineStr"/>
+      <c r="J13" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>V-11</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>launch_plan.csv</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>All NPI rows approval_status = APPROVED</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>status = APPROVED only</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>0 PENDING rows affect forecast</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr"/>
-      <c r="H14" s="9">
+      <c r="G14" s="17" t="inlineStr"/>
+      <c r="H14" s="11">
         <f>IF(G14="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G14)),G14="0",G14="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G14)),ISNUMBER(SEARCH("FAIL",G14))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Empty file = PASS (no NPI uplift applied).</t>
         </is>
       </c>
+      <c r="J14" s="39" t="inlineStr">
+        <is>
+          <t>WARNING — unapproved NPIs excluded from tentative</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>V-12</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>launch_plan.csv</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>launch_month in YYYY-MM format</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>regex \d{4}-\d{2}</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>All rows match</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr"/>
-      <c r="H15" s="9">
+      <c r="G15" s="17" t="inlineStr"/>
+      <c r="H15" s="11">
         <f>IF(G15="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G15)),G15="0",G15="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G15)),ISNUMBER(SEARCH("FAIL",G15))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I15" s="10" t="inlineStr"/>
+      <c r="I15" s="12" t="inlineStr"/>
+      <c r="J15" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>V-13</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>launch_plan.csv</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>No negative uplift percentages</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>month_N_uplift_pct &gt;= 0</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>0 negative values</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr"/>
-      <c r="H16" s="9">
+      <c r="G16" s="17" t="inlineStr"/>
+      <c r="H16" s="11">
         <f>IF(G16="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G16)),G16="0",G16="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G16)),ISNUMBER(SEARCH("FAIL",G16))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I16" s="8" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>V-14</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>fact_margin.csv</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>No ESTIMATED rows</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>quality_status != ESTIMATED</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>0 ESTIMATED rows</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr"/>
-      <c r="H17" s="9">
+      <c r="G17" s="17" t="inlineStr"/>
+      <c r="H17" s="11">
         <f>IF(G17="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G17)),G17="0",G17="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G17)),ISNUMBER(SEARCH("FAIL",G17))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>Currently 933 ESTIMATED rows — placeholder values.</t>
         </is>
       </c>
+      <c r="J17" s="39" t="inlineStr">
+        <is>
+          <t>WARNING — ESTIMATED margins used as LOW-confidence fallback</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>V-15</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>fact_margin.csv</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>approval_status column present</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Column exists</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Column found</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr"/>
-      <c r="H18" s="9">
+      <c r="G18" s="17" t="inlineStr"/>
+      <c r="H18" s="11">
         <f>IF(G18="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G18)),G18="0",G18="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G18)),ISNUMBER(SEARCH("FAIL",G18))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Add approval_status column; Finance marks FINANCE_APPROVED.</t>
         </is>
       </c>
+      <c r="J18" s="39" t="inlineStr">
+        <is>
+          <t>WARNING — Finance approval not required for tentative</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>V-16a</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>fact_margin.csv</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>No negative mrp</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>mrp &gt; 0</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>0 negative MRP rows</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr"/>
-      <c r="H19" s="9">
+      <c r="G19" s="17" t="inlineStr"/>
+      <c r="H19" s="11">
         <f>IF(G19="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G19)),G19="0",G19="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G19)),ISNUMBER(SEARCH("FAIL",G19))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I19" s="10" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr"/>
+      <c r="J19" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>V-16b</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>fact_margin.csv</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>No negative margin_pct</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>margin_pct &gt;= 0</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>0 negative rows</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr"/>
-      <c r="H20" s="9">
+      <c r="G20" s="17" t="inlineStr"/>
+      <c r="H20" s="11">
         <f>IF(G20="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G20)),G20="0",G20="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G20)),ISNUMBER(SEARCH("FAIL",G20))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Currently 2 negative rows (VMM chain) — see MARGIN_STATUS sheet.</t>
         </is>
       </c>
+      <c r="J20" s="39" t="inlineStr">
+        <is>
+          <t>WARNING — VMM rows isolated and excluded from tentative</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>V-16c</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>fact_margin.csv</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>No negative cm2_pct</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>cm2_pct &gt;= 0</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>0 negative rows</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr"/>
-      <c r="H21" s="9">
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="11">
         <f>IF(G21="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G21)),G21="0",G21="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G21)),ISNUMBER(SEARCH("FAIL",G21))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I21" s="10" t="inlineStr"/>
+      <c r="I21" s="12" t="inlineStr"/>
+      <c r="J21" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>V-17</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>fact_margin.csv</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>No duplicate month × chain × ean</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Deduplication check</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>0 duplicates</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr"/>
-      <c r="H22" s="9">
+      <c r="G22" s="17" t="inlineStr"/>
+      <c r="H22" s="11">
         <f>IF(G22="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G22)),G22="0",G22="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G22)),ISNUMBER(SEARCH("FAIL",G22))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Currently 0 duplicates ✓</t>
         </is>
       </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>BLOCKED (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>V-18</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>fact_margin.csv</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>mrp &gt; 0 for all rows</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>mrp &gt; 0</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>0 zero-MRP rows</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr"/>
-      <c r="H23" s="9">
+      <c r="G23" s="17" t="inlineStr"/>
+      <c r="H23" s="11">
         <f>IF(G23="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G23)),G23="0",G23="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G23)),ISNUMBER(SEARCH("FAIL",G23))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I23" s="10" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>V-19</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>cross-file</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>All target EANs exist in fact_margin</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>EAN cross-reference check</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>0 unmapped EANs</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr"/>
-      <c r="H24" s="9">
+      <c r="G24" s="17" t="inlineStr"/>
+      <c r="H24" s="11">
         <f>IF(G24="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G24)),G24="0",G24="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G24)),ISNUMBER(SEARCH("FAIL",G24))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I24" s="8" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="36" t="inlineStr">
+        <is>
+          <t>FAIL (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>V-20</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>all files</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>No excluded brands (Pure Origin, Lumineve, Staze)</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>brand NOT IN excluded list</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>0 excluded brand rows</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr"/>
-      <c r="H25" s="9">
+      <c r="G25" s="17" t="inlineStr"/>
+      <c r="H25" s="11">
         <f>IF(G25="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G25)),G25="0",G25="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G25)),ISNUMBER(SEARCH("FAIL",G25))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>Hard rule — never appears in forecast.</t>
         </is>
       </c>
+      <c r="J25" s="36" t="inlineStr">
+        <is>
+          <t>BLOCKED (structural — always enforced)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>V-21</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>offtake_history.csv</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>0 unmapped EANs (5 currently open)</t>
         </is>
       </c>
-      <c r="D26" s="31" t="inlineStr">
+      <c r="D26" s="40" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Audit unmapped EAN register</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>All 5 EANs resolved</t>
         </is>
       </c>
-      <c r="G26" s="15" t="inlineStr"/>
-      <c r="H26" s="9">
+      <c r="G26" s="17" t="inlineStr"/>
+      <c r="H26" s="11">
         <f>IF(G26="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G26)),G26="0",G26="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G26)),ISNUMBER(SEARCH("FAIL",G26))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>See UNMAPPED_EANS sheet.</t>
         </is>
       </c>
+      <c r="J26" s="39" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>V-22</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>primary_history.csv</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>No duplicate month × chain × ean</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Deduplication check</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>0 duplicates (currently 0 ✓)</t>
         </is>
       </c>
-      <c r="G27" s="15" t="inlineStr"/>
-      <c r="H27" s="9">
+      <c r="G27" s="17" t="inlineStr"/>
+      <c r="H27" s="11">
         <f>IF(G27="","PENDING",IF(OR(ISNUMBER(SEARCH("PASS",G27)),G27="0",G27="✓"),"PASS",IF(OR(ISNUMBER(SEARCH("BLOCKED",G27)),ISNUMBER(SEARCH("FAIL",G27))),"BLOCKED","REVIEW")))</f>
         <v/>
       </c>
-      <c r="I27" s="10" t="inlineStr"/>
+      <c r="I27" s="12" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>BLOCKED (structural)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>OVERALL GATE RESULT (live formula — auto-updates when col G is filled)</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-      <c r="G29" s="24" t="n"/>
-      <c r="H29" s="24" t="n"/>
-      <c r="I29" s="16" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Checks run</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>FAIL count</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>OVERALL STATUS</t>
         </is>
       </c>
+      <c r="J30" s="7" t="inlineStr"/>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="17">
+      <c r="A31" s="24">
         <f>COUNTA(A4:A27)</f>
         <v/>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="24">
         <f>COUNTIF(H4:H27,"PASS")</f>
         <v/>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="24">
         <f>COUNTIF(H4:H27,"REVIEW")</f>
         <v/>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="24">
         <f>COUNTIF(H4:H27,"PENDING")</f>
         <v/>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="24">
         <f>COUNTIF(H4:H27,"BLOCKED")</f>
         <v/>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="24">
         <f>COUNTIFS(D4:D27,"FAIL",H4:H27,"&lt;&gt;PASS")</f>
         <v/>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="24">
         <f>COUNTIFS(D4:D27,"WARNING",H4:H27,"&lt;&gt;PASS")</f>
         <v/>
       </c>
-      <c r="H31" s="17" t="inlineStr"/>
-      <c r="I31" s="32">
-        <f>IF(COUNTIF(H4:H27,"BLOCKED")&gt;0,"🔴 FORECAST BLOCKED — "&amp;COUNTIF(H4:H27,"BLOCKED")&amp;" BLOCKED",IF(COUNTIF(H4:H27,"REVIEW")&gt;0,"🟡 NEEDS REVIEW — "&amp;COUNTIF(H4:H27,"REVIEW")&amp;" checks need attention",IF(COUNTIF(H4:H27,"PENDING")&gt;0,"⏳ PENDING — fill col G with actual results","🟢 SAFE — run python refresh_forecast.py --months 3")))</f>
-        <v/>
-      </c>
+      <c r="H31" s="24" t="inlineStr"/>
+      <c r="I31" s="9">
+        <f>IF(COUNTIF(H4:H27,"BLOCKED")&gt;0,"FORECAST BLOCKED — "&amp;COUNTIF(H4:H27,"BLOCKED")&amp;" BLOCKED",IF(COUNTIF(H4:H27,"REVIEW")&gt;0,"NEEDS REVIEW — "&amp;COUNTIF(H4:H27,"REVIEW")&amp;" checks need attention",IF(COUNTIF(H4:H27,"PENDING")&gt;0,"PENDING — fill col G with actual results","SAFE — run python refresh_forecast.py --months 3")))</f>
+        <v/>
+      </c>
+      <c r="J31" s="41" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I27"/>
+  <autoFilter ref="A3:J27"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6917,7 +6877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6927,68 +6887,68 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>COMMAND REFERENCE  |  Exact commands to run at each stage</t>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>COMMAND REFERENCE  |  Exact commands to run at each stage  |  TENTATIVE = planning mode  |  FINAL = production</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Expected Output / Pass Criterion</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>STEP 1
 Unit tests
 (any time)</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>python -m forecast_engine.selftest</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>Ran 20 tests in ~0.04s
 OK
 → Must be 20/20</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>Run after any code change. Zero tolerance — 20/20 always.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>STEP 2
 Data readiness audit</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>python forecast_engine/data_readiness_audit.py
   --primary Phase_A_Input/primary_history.csv
@@ -6996,7 +6956,7 @@
   --margin  Phase_A_Input/fact_margin.csv</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>gate_status: PASS
 BLOCKED: 0
@@ -7004,54 +6964,122 @@
 → Output: audit_output/audit_summary.json</t>
         </is>
       </c>
-      <c r="D4" s="35" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>Run after any Phase_A_Input file changes. BLOCKED &gt; 0 = hard stop.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="33" t="inlineStr">
-        <is>
-          <t>STEP 3
-Business input validator</t>
-        </is>
-      </c>
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>python validate_business_inputs.py --mode full
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>STEP 3a
+Business validator
+(TENTATIVE mode)</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>python validate_business_inputs.py --mode tentative
+# With JSON output:
+python validate_business_inputs.py --mode tentative
+  --out validation_results_tentative.json</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>SAFE TO RUN TENTATIVE FORECAST WITH WARNINGS
+Exit code 0
+→ Approval gates relaxed; structural checks still enforced.</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>Run first to plan with available data.
+Outputs labeled is_tentative=True.
+Not for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>STEP 3b
+Business validator
+(FINAL mode)</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>python validate_business_inputs.py --mode final
 # Write JSON report:
-python validate_business_inputs.py --mode full
-  --out validation_results.json</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
+python validate_business_inputs.py --mode final
+  --out validation_results_final.json</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>RESULTS:  PASS=22  WARNING=0  FAIL=0  BLOCKED=0
 → Must see: safe to run refresh_forecast.py
 → Exit code 0</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>Must clear ALL BLOCKED and FAIL before Step 4.
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>Must clear ALL BLOCKED and FAIL before Step 4 (FINAL).
 Currently: BLOCKED=3 FAIL=2 — resolve business inputs first.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>STEP 4
-Production forecast</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="inlineStr">
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>STEP 4a
+Tentative forecast
+(planning only)</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>python -m forecast_engine.cli
+  --margin-repo margin_repository
+  --primary-data Phase_A_Input/primary_history.csv
+  --offtake-data Phase_A_Input/offtake_history.csv
+  --out forecast_outputs/tentative
+  --mode tentative
+  --months 3</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>TENTATIVE OUTPUTS — is_tentative=True
+→ Includes value_source, fallback_method,
+  confidence_level traceability fields
+→ VMM chain excluded (confidence_level=EXCLUDED)</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>For planning and alignment only.
+Do NOT use tentative outputs for finance reporting.
+Re-run in FINAL mode after all approvals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>STEP 4b
+Production forecast
+(FINAL mode)</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>python refresh_forecast.py --months 3 --verbose</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>PRODUCTION_READY
 9,138+ forecast records
@@ -7059,21 +7087,21 @@
 → Output: forecast_outputs/&lt;run_id&gt;/</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
-        <is>
-          <t>Only run after Steps 1–3 return all-clear.
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>Only run after Steps 1–3b return all-clear.
 Do NOT run with BLOCKED or FAIL in Steps 1–3.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>STEP 5
 Verify event uplifts</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>python -c "
 import pandas as pd
@@ -7083,7 +7111,7 @@
 "</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>Aug: mean &gt; 0 (Raksha Bandhan)
 Sep: mean = 0
@@ -7091,20 +7119,20 @@
 → Replace &lt;run_id&gt; with actual dir</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Verify approved uplifts are being applied. festival_uplift &gt; 0 for event months.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>STEP 6
 Warehouse reconciliation</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>python -c "
 import pandas as pd
@@ -7117,27 +7145,27 @@
 "</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>Max mismatch: &lt; 0.1
 Rows with mismatch: 0
 → Warehouse sum must equal forecast_primary_qty</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>Gate 5 already checks this; run manually to confirm.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="33" t="inlineStr">
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>STEP 7
 Update evidence</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t># After a successful approved run:
 git add PHASE_A_VALIDATION_EVIDENCE.md
@@ -7146,32 +7174,32 @@
 git push -u origin &lt;branch&gt;</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C11" s="42" t="inlineStr">
         <is>
           <t>Evidence file and tracker pushed to branch</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Update PHASE_A_VALIDATION_EVIDENCE.md with new run details. Keep tracker current.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>STEP 8
 Backtesting
 (once ≥3 months offtake)</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>python forecast_engine/backtesting_framework.py
   Phase_A_Input backtest_output</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C12" s="44" t="inlineStr">
         <is>
           <t>WAPE Total MT ≤ 10%
 WAPE Chain ≤ 15%
@@ -7179,7 +7207,7 @@
 Forecast Bias within ±5%</t>
         </is>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D12" s="44" t="inlineStr">
         <is>
           <t>Currently only 2 months of offtake (Apr–May 2026). Re-run when Jun 2026 offtake is loaded.</t>
         </is>
